--- a/premise/data/additional_inventories/lci-batteries-SIB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-SIB.xlsx
@@ -16,7 +16,7 @@
     <sheet name="sodium-ion batteries" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'sodium-ion batteries'!$A$1:$K$480</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'sodium-ion batteries'!$A$1:$K$481</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1264,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K516"/>
+  <dimension ref="A1:K517"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" customWidth="1"/>
@@ -3660,8 +3660,10 @@
       <c r="A159" t="s">
         <v>2</v>
       </c>
-      <c r="B159" t="s">
-        <v>221</v>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Source: Zhang, S., Steubing, B., Potter, H. K., Hansson, P. A., &amp; Nordberg, Å. (2024). Future climate impacts of sodium-ion batteries. Resources, Conservation and Recycling, 202, 107362. https://doi.org/10.1016/j.resconrec.2023.107362 Local inventory correction, 2026-10-17 (approved): restore the NMMT cathode aluminium current collector reported by Zhang et al. (2024), DOI 10.1016/j.resconrec.2023.107362, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344923004962-mmc2.xlsx, sheet inventory_chemical, D23 = 2.4090925790870865 kg foil per D29 = 20.99776988685781 kg cathode batch (0.11473087818696887 kg foil/kg cathode). The original batch basis is retained: this exchange is a batch input, not a per-kg input. Active material D18 + binder D19 + carbon D20 + collector D23 reproduce the cathode output D29. The anode has a separate collector already included in its own inventory; this correction restores only the omitted cathode collector. Cell input, cell mass, electricity, transport and other recipes are retained. This restores one documented material omission and does not validate the complete battery design or lifetime.</t>
+        </is>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -3734,6 +3736,11 @@
       <c r="H166" t="s">
         <v>5</v>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
@@ -3939,142 +3946,159 @@
         <v>34</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>market for aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>2.4090925790870865</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>ei_3.9.1_cutoff</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Local inventory correction, 2026-10-17 (approved): restore the NMMT cathode aluminium current collector reported by Zhang et al. (2024), DOI 10.1016/j.resconrec.2023.107362, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344923004962-mmc2.xlsx, sheet inventory_chemical, D23 = 2.4090925790870865 kg foil per D29 = 20.99776988685781 kg cathode batch (0.11473087818696887 kg foil/kg cathode). The original batch basis is retained: this exchange is a batch input, not a per-kg input. Active material D18 + binder D19 + carbon D20 + collector D23 reproduce the cathode output D29. The anode has a separate collector already included in its own inventory; this correction restores only the omitted cathode collector. Cell input, cell mass, electricity, transport and other recipes are retained. This restores one documented material omission and does not validate the complete battery design or lifetime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B177" s="1" t="s">
+      <c r="B178" s="1" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>2</v>
-      </c>
-      <c r="B178" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B179" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B180" t="s">
-        <v>186</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B181" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B182" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>6</v>
+      </c>
+      <c r="B183" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
         <v>216</v>
       </c>
-      <c r="B183" t="s">
+      <c r="B184" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>9</v>
-      </c>
-      <c r="B185" t="s">
-        <v>10</v>
-      </c>
-      <c r="C185" t="s">
-        <v>11</v>
-      </c>
-      <c r="D185" t="s">
-        <v>3</v>
-      </c>
-      <c r="E185" t="s">
-        <v>6</v>
-      </c>
-      <c r="F185" t="s">
-        <v>12</v>
-      </c>
-      <c r="G185" t="s">
-        <v>13</v>
-      </c>
-      <c r="H185" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>14</v>
-      </c>
-      <c r="B186">
-        <v>151.38073881302458</v>
+        <v>9</v>
+      </c>
+      <c r="B186" t="s">
+        <v>10</v>
       </c>
       <c r="C186" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D186" t="s">
+        <v>3</v>
       </c>
       <c r="E186" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F186" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G186" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H186" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="B187">
-        <v>13.018168247328598</v>
+        <v>151.38073881302458</v>
       </c>
       <c r="C187" t="s">
-        <v>164</v>
-      </c>
-      <c r="D187" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E187" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="F187" t="s">
+        <v>16</v>
       </c>
       <c r="G187" t="s">
-        <v>18</v>
-      </c>
-      <c r="H187" t="s">
-        <v>186</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B188">
-        <v>0.55460691116478344</v>
+        <v>13.018168247328598</v>
       </c>
       <c r="C188" t="s">
         <v>164</v>
@@ -4086,18 +4110,18 @@
         <v>7</v>
       </c>
       <c r="G188" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H188" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B189">
-        <v>10.204767165432015</v>
+        <v>0.55460691116478344</v>
       </c>
       <c r="C189" t="s">
         <v>164</v>
@@ -4112,21 +4136,21 @@
         <v>19</v>
       </c>
       <c r="H189" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="B190">
-        <v>1.9260300240329271</v>
+        <v>10.204767165432015</v>
       </c>
       <c r="C190" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D190" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E190" t="s">
         <v>7</v>
@@ -4135,15 +4159,15 @@
         <v>19</v>
       </c>
       <c r="H190" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B191">
-        <v>0.33276414669887006</v>
+        <v>1.9260300240329271</v>
       </c>
       <c r="C191" t="s">
         <v>165</v>
@@ -4158,38 +4182,38 @@
         <v>19</v>
       </c>
       <c r="H191" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B192">
-        <v>1.3018168247328599</v>
+        <v>0.33276414669887006</v>
       </c>
       <c r="C192" t="s">
         <v>165</v>
       </c>
       <c r="D192" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E192" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G192" t="s">
         <v>19</v>
       </c>
       <c r="H192" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B193">
-        <v>42.050205225840159</v>
+        <v>1.3018168247328599</v>
       </c>
       <c r="C193" t="s">
         <v>165</v>
@@ -4198,152 +4222,155 @@
         <v>4</v>
       </c>
       <c r="E193" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G193" t="s">
         <v>19</v>
       </c>
       <c r="H193" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>25</v>
+      </c>
+      <c r="B194">
+        <v>42.050205225840159</v>
+      </c>
+      <c r="C194" t="s">
+        <v>165</v>
+      </c>
+      <c r="D194" t="s">
+        <v>4</v>
+      </c>
+      <c r="E194" t="s">
+        <v>26</v>
+      </c>
+      <c r="G194" t="s">
+        <v>19</v>
+      </c>
+      <c r="H194" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
         <v>27</v>
       </c>
-      <c r="B194">
+      <c r="B195">
         <v>7.8109009483971592</v>
       </c>
-      <c r="C194" t="s">
-        <v>165</v>
-      </c>
-      <c r="D194" t="s">
-        <v>4</v>
-      </c>
-      <c r="E194" t="s">
+      <c r="C195" t="s">
+        <v>165</v>
+      </c>
+      <c r="D195" t="s">
+        <v>4</v>
+      </c>
+      <c r="E195" t="s">
         <v>24</v>
       </c>
-      <c r="G194" t="s">
-        <v>19</v>
-      </c>
-      <c r="H194" t="s">
+      <c r="G195" t="s">
+        <v>19</v>
+      </c>
+      <c r="H195" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="1" t="s">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B196" s="1" t="s">
+      <c r="B197" s="1" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>2</v>
-      </c>
-      <c r="B197" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B199" t="s">
-        <v>105</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>7</v>
+        <v>105</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>6</v>
+      </c>
+      <c r="B201" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
         <v>216</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B202" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="1" t="s">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>9</v>
-      </c>
-      <c r="B203" t="s">
-        <v>10</v>
-      </c>
-      <c r="C203" t="s">
-        <v>11</v>
-      </c>
-      <c r="D203" t="s">
-        <v>3</v>
-      </c>
-      <c r="E203" t="s">
-        <v>6</v>
-      </c>
-      <c r="F203" t="s">
-        <v>12</v>
-      </c>
-      <c r="G203" t="s">
-        <v>13</v>
-      </c>
-      <c r="H203" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>14</v>
-      </c>
-      <c r="B204">
-        <v>1.98E-3</v>
+        <v>9</v>
+      </c>
+      <c r="B204" t="s">
+        <v>10</v>
       </c>
       <c r="C204" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D204" t="s">
+        <v>3</v>
       </c>
       <c r="E204" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F204" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G204" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H204" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B205">
-        <v>-7.4999999999999997E-2</v>
+        <v>1.98E-3</v>
       </c>
       <c r="C205" t="s">
         <v>31</v>
       </c>
       <c r="E205" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F205" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="G205" t="s">
         <v>17</v>
@@ -4351,10 +4378,10 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="B206">
-        <v>7.4999999999999997E-2</v>
+        <v>-7.4999999999999997E-2</v>
       </c>
       <c r="C206" t="s">
         <v>31</v>
@@ -4363,7 +4390,7 @@
         <v>57</v>
       </c>
       <c r="F206" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="G206" t="s">
         <v>17</v>
@@ -4371,33 +4398,30 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="B207">
-        <v>0.18852782774999999</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C207" t="s">
-        <v>164</v>
-      </c>
-      <c r="D207" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E207" t="s">
-        <v>7</v>
+        <v>57</v>
+      </c>
+      <c r="F207" t="s">
+        <v>107</v>
       </c>
       <c r="G207" t="s">
-        <v>18</v>
-      </c>
-      <c r="H207" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="B208">
-        <v>0.13861725499999999</v>
+        <v>0.18852782774999999</v>
       </c>
       <c r="C208" t="s">
         <v>164</v>
@@ -4409,21 +4433,21 @@
         <v>7</v>
       </c>
       <c r="G208" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H208" t="s">
-        <v>209</v>
+        <v>105</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="B209">
-        <v>7.7348066002303498E-2</v>
+        <v>0.13861725499999999</v>
       </c>
       <c r="C209" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D209" t="s">
         <v>4</v>
@@ -4435,21 +4459,21 @@
         <v>19</v>
       </c>
       <c r="H209" t="s">
-        <v>74</v>
+        <v>209</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>108</v>
+        <v>257</v>
       </c>
       <c r="B210">
-        <v>5.9833142249999999E-2</v>
+        <v>7.7348066002303498E-2</v>
       </c>
       <c r="C210" t="s">
         <v>165</v>
       </c>
       <c r="D210" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E210" t="s">
         <v>7</v>
@@ -4458,38 +4482,38 @@
         <v>19</v>
       </c>
       <c r="H210" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="B211">
-        <v>5.9833142250000004E-3</v>
+        <v>5.9833142249999999E-2</v>
       </c>
       <c r="C211" t="s">
         <v>165</v>
       </c>
       <c r="D211" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E211" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G211" t="s">
         <v>19</v>
       </c>
       <c r="H211" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="B212">
-        <v>1.9777030709528598E-3</v>
+        <v>5.9833142250000004E-3</v>
       </c>
       <c r="C212" t="s">
         <v>165</v>
@@ -4498,21 +4522,21 @@
         <v>4</v>
       </c>
       <c r="E212" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G212" t="s">
         <v>19</v>
       </c>
       <c r="H212" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="B213">
-        <v>-9.9225694999999798E-3</v>
+        <v>1.9777030709528598E-3</v>
       </c>
       <c r="C213" t="s">
         <v>165</v>
@@ -4521,166 +4545,166 @@
         <v>4</v>
       </c>
       <c r="E213" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G213" t="s">
         <v>19</v>
       </c>
       <c r="H213" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>110</v>
+      </c>
+      <c r="B214">
+        <v>-9.9225694999999798E-3</v>
+      </c>
+      <c r="C214" t="s">
+        <v>165</v>
+      </c>
+      <c r="D214" t="s">
+        <v>4</v>
+      </c>
+      <c r="E214" t="s">
+        <v>7</v>
+      </c>
+      <c r="G214" t="s">
+        <v>19</v>
+      </c>
+      <c r="H214" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
         <v>27</v>
       </c>
-      <c r="B214">
+      <c r="B215">
         <v>3.5899885350000001E-2</v>
       </c>
-      <c r="C214" t="s">
-        <v>165</v>
-      </c>
-      <c r="D214" t="s">
-        <v>4</v>
-      </c>
-      <c r="E214" t="s">
+      <c r="C215" t="s">
+        <v>165</v>
+      </c>
+      <c r="D215" t="s">
+        <v>4</v>
+      </c>
+      <c r="E215" t="s">
         <v>24</v>
       </c>
-      <c r="G214" t="s">
-        <v>19</v>
-      </c>
-      <c r="H214" t="s">
+      <c r="G215" t="s">
+        <v>19</v>
+      </c>
+      <c r="H215" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="1" t="s">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="B217" s="1" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>2</v>
-      </c>
-      <c r="B217" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B218" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B219" t="s">
-        <v>189</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B220" t="s">
-        <v>7</v>
+        <v>189</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>6</v>
+      </c>
+      <c r="B221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
         <v>216</v>
       </c>
-      <c r="B221" t="s">
+      <c r="B222" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="1" t="s">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>9</v>
-      </c>
-      <c r="B223" t="s">
-        <v>10</v>
-      </c>
-      <c r="C223" t="s">
-        <v>11</v>
-      </c>
-      <c r="D223" t="s">
-        <v>3</v>
-      </c>
-      <c r="E223" t="s">
-        <v>6</v>
-      </c>
-      <c r="F223" t="s">
-        <v>12</v>
-      </c>
-      <c r="G223" t="s">
-        <v>13</v>
-      </c>
-      <c r="H223" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>14</v>
-      </c>
-      <c r="B224">
-        <v>627.8620554092613</v>
+        <v>9</v>
+      </c>
+      <c r="B224" t="s">
+        <v>10</v>
       </c>
       <c r="C224" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D224" t="s">
+        <v>3</v>
       </c>
       <c r="E224" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F224" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G224" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H224" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>188</v>
+        <v>14</v>
       </c>
       <c r="B225">
-        <v>21.612062241046353</v>
+        <v>627.8620554092613</v>
       </c>
       <c r="C225" t="s">
-        <v>164</v>
-      </c>
-      <c r="D225" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E225" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="F225" t="s">
+        <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>18</v>
-      </c>
-      <c r="H225" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="B226">
-        <v>0.39372064434026838</v>
+        <v>21.612062241046353</v>
       </c>
       <c r="C226" t="s">
         <v>164</v>
@@ -4692,18 +4716,18 @@
         <v>7</v>
       </c>
       <c r="G226" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H226" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B227">
-        <v>18.898590928332883</v>
+        <v>0.39372064434026838</v>
       </c>
       <c r="C227" t="s">
         <v>164</v>
@@ -4718,21 +4742,21 @@
         <v>19</v>
       </c>
       <c r="H227" t="s">
-        <v>105</v>
+        <v>176</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="B228">
-        <v>1.9260300240329271</v>
+        <v>18.898590928332883</v>
       </c>
       <c r="C228" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D228" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E228" t="s">
         <v>7</v>
@@ -4741,15 +4765,15 @@
         <v>19</v>
       </c>
       <c r="H228" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B229">
-        <v>0.39372064434026838</v>
+        <v>1.9260300240329271</v>
       </c>
       <c r="C229" t="s">
         <v>165</v>
@@ -4764,38 +4788,38 @@
         <v>19</v>
       </c>
       <c r="H229" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B230">
-        <v>3.1061357705212793</v>
+        <v>0.39372064434026838</v>
       </c>
       <c r="C230" t="s">
         <v>165</v>
       </c>
       <c r="D230" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E230" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G230" t="s">
         <v>19</v>
       </c>
       <c r="H230" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B231">
-        <v>74.629587023119612</v>
+        <v>3.1061357705212793</v>
       </c>
       <c r="C231" t="s">
         <v>165</v>
@@ -4804,13 +4828,13 @@
         <v>4</v>
       </c>
       <c r="E231" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G231" t="s">
         <v>19</v>
       </c>
       <c r="H231" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
@@ -4818,7 +4842,7 @@
         <v>25</v>
       </c>
       <c r="B232">
-        <v>99.776539479452978</v>
+        <v>74.629587023119612</v>
       </c>
       <c r="C232" t="s">
         <v>165</v>
@@ -4838,140 +4862,143 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>25</v>
+      </c>
+      <c r="B233">
+        <v>99.776539479452978</v>
+      </c>
+      <c r="C233" t="s">
+        <v>165</v>
+      </c>
+      <c r="D233" t="s">
+        <v>4</v>
+      </c>
+      <c r="E233" t="s">
+        <v>26</v>
+      </c>
+      <c r="G233" t="s">
+        <v>19</v>
+      </c>
+      <c r="H233" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
         <v>27</v>
       </c>
-      <c r="B233">
+      <c r="B234">
         <v>18.636814623127677</v>
       </c>
-      <c r="C233" t="s">
-        <v>165</v>
-      </c>
-      <c r="D233" t="s">
-        <v>4</v>
-      </c>
-      <c r="E233" t="s">
+      <c r="C234" t="s">
+        <v>165</v>
+      </c>
+      <c r="D234" t="s">
+        <v>4</v>
+      </c>
+      <c r="E234" t="s">
         <v>24</v>
       </c>
-      <c r="G233" t="s">
-        <v>19</v>
-      </c>
-      <c r="H233" t="s">
+      <c r="G234" t="s">
+        <v>19</v>
+      </c>
+      <c r="H234" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B235" s="1" t="s">
+      <c r="B236" s="1" t="s">
         <v>190</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>2</v>
-      </c>
-      <c r="B236" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B237" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B238" t="s">
-        <v>191</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B239" t="s">
-        <v>28</v>
+        <v>191</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B240" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
+        <v>6</v>
+      </c>
+      <c r="B241" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
         <v>216</v>
       </c>
-      <c r="B241" t="s">
+      <c r="B242" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A242" s="1" t="s">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>9</v>
-      </c>
-      <c r="B243" t="s">
-        <v>10</v>
-      </c>
-      <c r="C243" t="s">
-        <v>11</v>
-      </c>
-      <c r="D243" t="s">
-        <v>3</v>
-      </c>
-      <c r="E243" t="s">
-        <v>6</v>
-      </c>
-      <c r="F243" t="s">
-        <v>12</v>
-      </c>
-      <c r="G243" t="s">
-        <v>13</v>
-      </c>
-      <c r="H243" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>112</v>
-      </c>
-      <c r="B244">
-        <v>2.496E-3</v>
+        <v>9</v>
+      </c>
+      <c r="B244" t="s">
+        <v>10</v>
       </c>
       <c r="C244" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D244" t="s">
+        <v>3</v>
       </c>
       <c r="E244" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F244" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G244" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H244" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="B245">
-        <v>0.36174000000000001</v>
+        <v>2.496E-3</v>
       </c>
       <c r="C245" t="s">
         <v>31</v>
@@ -4988,10 +5015,10 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="B246">
-        <v>0.01</v>
+        <v>0.36174000000000001</v>
       </c>
       <c r="C246" t="s">
         <v>31</v>
@@ -5008,10 +5035,10 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B247">
-        <v>1.279E-3</v>
+        <v>0.01</v>
       </c>
       <c r="C247" t="s">
         <v>31</v>
@@ -5028,16 +5055,16 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="B248">
-        <v>1.8699999999999999E-4</v>
+        <v>1.279E-3</v>
       </c>
       <c r="C248" t="s">
         <v>31</v>
       </c>
       <c r="E248" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="F248" t="s">
         <v>16</v>
@@ -5048,62 +5075,59 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="B249">
-        <v>1</v>
+        <v>1.8699999999999999E-4</v>
       </c>
       <c r="C249" t="s">
-        <v>164</v>
-      </c>
-      <c r="D249" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E249" t="s">
-        <v>7</v>
+        <v>57</v>
+      </c>
+      <c r="F249" t="s">
+        <v>16</v>
       </c>
       <c r="G249" t="s">
-        <v>18</v>
-      </c>
-      <c r="H249" t="s">
-        <v>191</v>
+        <v>17</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="B250">
-        <v>0.19777800000000001</v>
+        <v>1</v>
       </c>
       <c r="C250" t="s">
         <v>164</v>
       </c>
       <c r="D250" t="s">
-        <v>115</v>
+        <v>4</v>
       </c>
       <c r="E250" t="s">
         <v>7</v>
       </c>
       <c r="G250" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H250" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>257</v>
+        <v>207</v>
       </c>
       <c r="B251">
-        <v>0.79940900000000004</v>
+        <v>0.19777800000000001</v>
       </c>
       <c r="C251" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D251" t="s">
-        <v>4</v>
+        <v>115</v>
       </c>
       <c r="E251" t="s">
         <v>7</v>
@@ -5112,21 +5136,21 @@
         <v>19</v>
       </c>
       <c r="H251" t="s">
-        <v>74</v>
+        <v>206</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="B252">
-        <v>0.98708899999999999</v>
+        <v>0.79940900000000004</v>
       </c>
       <c r="C252" t="s">
         <v>165</v>
       </c>
       <c r="D252" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E252" t="s">
         <v>7</v>
@@ -5135,15 +5159,15 @@
         <v>19</v>
       </c>
       <c r="H252" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="B253">
-        <v>4.0000000000000001E-10</v>
+        <v>0.98708899999999999</v>
       </c>
       <c r="C253" t="s">
         <v>165</v>
@@ -5152,44 +5176,44 @@
         <v>21</v>
       </c>
       <c r="E253" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G253" t="s">
         <v>19</v>
       </c>
       <c r="H253" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="B254">
-        <v>0.01</v>
+        <v>4.0000000000000001E-10</v>
       </c>
       <c r="C254" t="s">
         <v>165</v>
       </c>
       <c r="D254" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E254" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G254" t="s">
         <v>19</v>
       </c>
       <c r="H254" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B255">
-        <v>0.65286200000000005</v>
+        <v>0.01</v>
       </c>
       <c r="C255" t="s">
         <v>165</v>
@@ -5204,21 +5228,21 @@
         <v>19</v>
       </c>
       <c r="H255" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B256">
-        <v>0.249969</v>
+        <v>0.65286200000000005</v>
       </c>
       <c r="C256" t="s">
         <v>165</v>
       </c>
       <c r="D256" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E256" t="s">
         <v>7</v>
@@ -5227,15 +5251,15 @@
         <v>19</v>
       </c>
       <c r="H256" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B257">
-        <v>0.63938200000000001</v>
+        <v>0.249969</v>
       </c>
       <c r="C257" t="s">
         <v>165</v>
@@ -5250,15 +5274,15 @@
         <v>19</v>
       </c>
       <c r="H257" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="B258">
-        <v>0.640934</v>
+        <v>0.63938200000000001</v>
       </c>
       <c r="C258" t="s">
         <v>165</v>
@@ -5273,44 +5297,44 @@
         <v>19</v>
       </c>
       <c r="H258" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="B259">
-        <v>2.2634189999999998</v>
+        <v>0.640934</v>
       </c>
       <c r="C259" t="s">
         <v>165</v>
       </c>
       <c r="D259" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E259" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G259" t="s">
         <v>19</v>
       </c>
       <c r="H259" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B260">
-        <v>0.40388299999999999</v>
+        <v>2.2634189999999998</v>
       </c>
       <c r="C260" t="s">
         <v>165</v>
       </c>
       <c r="D260" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E260" t="s">
         <v>24</v>
@@ -5319,200 +5343,203 @@
         <v>19</v>
       </c>
       <c r="H260" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="B261">
-        <v>-8.1999999999999998E-4</v>
+        <v>0.40388299999999999</v>
       </c>
       <c r="C261" t="s">
         <v>165</v>
       </c>
       <c r="D261" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E261" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G261" t="s">
         <v>19</v>
       </c>
       <c r="H261" t="s">
-        <v>58</v>
+        <v>128</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B262">
-        <v>5.0000000000000001E-3</v>
+        <v>-8.1999999999999998E-4</v>
       </c>
       <c r="C262" t="s">
         <v>165</v>
       </c>
       <c r="D262" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E262" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="G262" t="s">
         <v>19</v>
       </c>
       <c r="H262" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>25</v>
+      </c>
+      <c r="B263">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C263" t="s">
+        <v>165</v>
+      </c>
+      <c r="D263" t="s">
+        <v>4</v>
+      </c>
+      <c r="E263" t="s">
+        <v>26</v>
+      </c>
+      <c r="G263" t="s">
+        <v>19</v>
+      </c>
+      <c r="H263" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
         <v>81</v>
       </c>
-      <c r="B263">
+      <c r="B264">
         <v>15.561019999999999</v>
       </c>
-      <c r="C263" t="s">
-        <v>165</v>
-      </c>
-      <c r="D263" t="s">
-        <v>4</v>
-      </c>
-      <c r="E263" t="s">
+      <c r="C264" t="s">
+        <v>165</v>
+      </c>
+      <c r="D264" t="s">
+        <v>4</v>
+      </c>
+      <c r="E264" t="s">
         <v>15</v>
       </c>
-      <c r="G263" t="s">
-        <v>19</v>
-      </c>
-      <c r="H263" t="s">
+      <c r="G264" t="s">
+        <v>19</v>
+      </c>
+      <c r="H264" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A265" s="1" t="s">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B265" s="1" t="s">
+      <c r="B266" s="1" t="s">
         <v>181</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
-        <v>2</v>
-      </c>
-      <c r="B266" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B267" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B268" t="s">
-        <v>182</v>
+        <v>4</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B269" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B270" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
+        <v>6</v>
+      </c>
+      <c r="B271" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
         <v>216</v>
       </c>
-      <c r="B271" t="s">
+      <c r="B272" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A272" s="1" t="s">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A273" t="s">
-        <v>9</v>
-      </c>
-      <c r="B273" t="s">
-        <v>10</v>
-      </c>
-      <c r="C273" t="s">
-        <v>11</v>
-      </c>
-      <c r="D273" t="s">
-        <v>3</v>
-      </c>
-      <c r="E273" t="s">
-        <v>6</v>
-      </c>
-      <c r="F273" t="s">
-        <v>12</v>
-      </c>
-      <c r="G273" t="s">
-        <v>13</v>
-      </c>
-      <c r="H273" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>14</v>
-      </c>
-      <c r="B274">
-        <v>6.42</v>
+        <v>9</v>
+      </c>
+      <c r="B274" t="s">
+        <v>10</v>
       </c>
       <c r="C274" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D274" t="s">
+        <v>3</v>
       </c>
       <c r="E274" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F274" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G274" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H274" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="B275">
-        <v>1.63</v>
+        <v>6.42</v>
       </c>
       <c r="C275" t="s">
         <v>31</v>
       </c>
       <c r="E275" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="F275" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="G275" t="s">
         <v>17</v>
@@ -5520,62 +5547,59 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="B276">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="C276" t="s">
-        <v>164</v>
-      </c>
-      <c r="D276" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E276" t="s">
-        <v>7</v>
+        <v>90</v>
+      </c>
+      <c r="F276" t="s">
+        <v>91</v>
       </c>
       <c r="G276" t="s">
-        <v>18</v>
-      </c>
-      <c r="H276" t="s">
-        <v>182</v>
+        <v>17</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>92</v>
+        <v>181</v>
       </c>
       <c r="B277">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C277" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D277" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E277" t="s">
         <v>7</v>
       </c>
       <c r="G277" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H277" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B278">
-        <v>105.79</v>
+        <v>1.2</v>
       </c>
       <c r="C278" t="s">
         <v>165</v>
       </c>
       <c r="D278" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="E278" t="s">
         <v>7</v>
@@ -5584,38 +5608,38 @@
         <v>19</v>
       </c>
       <c r="H278" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="B279">
-        <v>0.12</v>
+        <v>105.79</v>
       </c>
       <c r="C279" t="s">
         <v>165</v>
       </c>
       <c r="D279" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E279" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G279" t="s">
         <v>19</v>
       </c>
       <c r="H279" t="s">
-        <v>33</v>
+        <v>95</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B280">
-        <v>1.78</v>
+        <v>0.12</v>
       </c>
       <c r="C280" t="s">
         <v>165</v>
@@ -5624,169 +5648,169 @@
         <v>4</v>
       </c>
       <c r="E280" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G280" t="s">
         <v>19</v>
       </c>
       <c r="H280" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>25</v>
+      </c>
+      <c r="B281">
+        <v>1.78</v>
+      </c>
+      <c r="C281" t="s">
+        <v>165</v>
+      </c>
+      <c r="D281" t="s">
+        <v>4</v>
+      </c>
+      <c r="E281" t="s">
+        <v>26</v>
+      </c>
+      <c r="G281" t="s">
+        <v>19</v>
+      </c>
+      <c r="H281" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
         <v>27</v>
       </c>
-      <c r="B281">
+      <c r="B282">
         <v>0.71699999999999997</v>
       </c>
-      <c r="C281" t="s">
-        <v>165</v>
-      </c>
-      <c r="D281" t="s">
-        <v>4</v>
-      </c>
-      <c r="E281" t="s">
+      <c r="C282" t="s">
+        <v>165</v>
+      </c>
+      <c r="D282" t="s">
+        <v>4</v>
+      </c>
+      <c r="E282" t="s">
         <v>24</v>
       </c>
-      <c r="G281" t="s">
-        <v>19</v>
-      </c>
-      <c r="H281" t="s">
+      <c r="G282" t="s">
+        <v>19</v>
+      </c>
+      <c r="H282" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A283" s="1" t="s">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B283" s="1" t="s">
+      <c r="B284" s="1" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>2</v>
-      </c>
-      <c r="B284" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B285" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B286" t="s">
-        <v>193</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B287" t="s">
-        <v>7</v>
+        <v>193</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>6</v>
+      </c>
+      <c r="B288" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
         <v>216</v>
       </c>
-      <c r="B288" t="s">
+      <c r="B289" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A289" s="1" t="s">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A290" t="s">
-        <v>9</v>
-      </c>
-      <c r="B290" t="s">
-        <v>10</v>
-      </c>
-      <c r="C290" t="s">
-        <v>11</v>
-      </c>
-      <c r="D290" t="s">
-        <v>3</v>
-      </c>
-      <c r="E290" t="s">
-        <v>6</v>
-      </c>
-      <c r="F290" t="s">
-        <v>12</v>
-      </c>
-      <c r="G290" t="s">
-        <v>13</v>
-      </c>
-      <c r="H290" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>14</v>
-      </c>
-      <c r="B291">
-        <v>125.30664747888518</v>
+        <v>9</v>
+      </c>
+      <c r="B291" t="s">
+        <v>10</v>
       </c>
       <c r="C291" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D291" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E291" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F291" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G291" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H291" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>192</v>
+        <v>14</v>
       </c>
       <c r="B292">
-        <v>10.958581208608772</v>
+        <v>125.30664747888518</v>
       </c>
       <c r="C292" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
       <c r="D292" t="s">
         <v>4</v>
       </c>
       <c r="E292" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="F292" t="s">
+        <v>16</v>
       </c>
       <c r="G292" t="s">
-        <v>18</v>
-      </c>
-      <c r="H292" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="B293">
-        <v>0.45837082374932231</v>
+        <v>10.958581208608772</v>
       </c>
       <c r="C293" t="s">
         <v>164</v>
@@ -5798,18 +5822,18 @@
         <v>7</v>
       </c>
       <c r="G293" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H293" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B294">
-        <v>8.4482150228766919</v>
+        <v>0.45837082374932231</v>
       </c>
       <c r="C294" t="s">
         <v>164</v>
@@ -5824,21 +5848,21 @@
         <v>19</v>
       </c>
       <c r="H294" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="B295">
-        <v>1.7769728677331647</v>
+        <v>8.4482150228766919</v>
       </c>
       <c r="C295" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D295" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E295" t="s">
         <v>7</v>
@@ -5847,15 +5871,15 @@
         <v>19</v>
       </c>
       <c r="H295" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B296">
-        <v>0.27502249424959335</v>
+        <v>1.7769728677331647</v>
       </c>
       <c r="C296" t="s">
         <v>165</v>
@@ -5870,38 +5894,38 @@
         <v>19</v>
       </c>
       <c r="H296" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B297">
-        <v>1.0958581208608771</v>
+        <v>0.27502249424959335</v>
       </c>
       <c r="C297" t="s">
         <v>165</v>
       </c>
       <c r="D297" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E297" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G297" t="s">
         <v>19</v>
       </c>
       <c r="H297" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B298">
-        <v>34.807402077468105</v>
+        <v>1.0958581208608771</v>
       </c>
       <c r="C298" t="s">
         <v>165</v>
@@ -5910,175 +5934,175 @@
         <v>4</v>
       </c>
       <c r="E298" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G298" t="s">
         <v>19</v>
       </c>
       <c r="H298" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
+        <v>25</v>
+      </c>
+      <c r="B299">
+        <v>34.807402077468105</v>
+      </c>
+      <c r="C299" t="s">
+        <v>165</v>
+      </c>
+      <c r="D299" t="s">
+        <v>4</v>
+      </c>
+      <c r="E299" t="s">
+        <v>26</v>
+      </c>
+      <c r="G299" t="s">
+        <v>19</v>
+      </c>
+      <c r="H299" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
         <v>27</v>
       </c>
-      <c r="B299">
+      <c r="B300">
         <v>6.5751487251652625</v>
       </c>
-      <c r="C299" t="s">
-        <v>165</v>
-      </c>
-      <c r="D299" t="s">
-        <v>4</v>
-      </c>
-      <c r="E299" t="s">
+      <c r="C300" t="s">
+        <v>165</v>
+      </c>
+      <c r="D300" t="s">
+        <v>4</v>
+      </c>
+      <c r="E300" t="s">
         <v>24</v>
       </c>
-      <c r="G299" t="s">
-        <v>19</v>
-      </c>
-      <c r="H299" t="s">
+      <c r="G300" t="s">
+        <v>19</v>
+      </c>
+      <c r="H300" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A302" s="1" t="s">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B302" s="1" t="s">
+      <c r="B303" s="1" t="s">
         <v>194</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>2</v>
-      </c>
-      <c r="B303" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
+        <v>2</v>
+      </c>
+      <c r="B304" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
         <v>3</v>
       </c>
-      <c r="B304" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>5</v>
-      </c>
       <c r="B305" t="s">
-        <v>129</v>
+        <v>4</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B306" t="s">
-        <v>7</v>
+        <v>129</v>
       </c>
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>6</v>
+      </c>
+      <c r="B307" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
         <v>216</v>
       </c>
-      <c r="B307" t="s">
+      <c r="B308" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A308" s="1" t="s">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A309" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>9</v>
-      </c>
-      <c r="B309" t="s">
-        <v>10</v>
-      </c>
-      <c r="C309" t="s">
-        <v>11</v>
-      </c>
-      <c r="D309" t="s">
-        <v>3</v>
-      </c>
-      <c r="E309" t="s">
-        <v>6</v>
-      </c>
-      <c r="F309" t="s">
-        <v>12</v>
-      </c>
-      <c r="G309" t="s">
-        <v>13</v>
-      </c>
-      <c r="H309" t="s">
-        <v>44</v>
-      </c>
-      <c r="I309" t="s">
-        <v>45</v>
-      </c>
-      <c r="J309" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>83</v>
-      </c>
-      <c r="B310">
-        <v>3.2919999999999998E-3</v>
+        <v>9</v>
+      </c>
+      <c r="B310" t="s">
+        <v>10</v>
       </c>
       <c r="C310" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D310" t="s">
+        <v>3</v>
       </c>
       <c r="E310" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="F310" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="G310" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H310" t="s">
+        <v>44</v>
+      </c>
+      <c r="I310" t="s">
+        <v>45</v>
+      </c>
+      <c r="J310" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="B311">
-        <v>1</v>
+        <v>3.2919999999999998E-3</v>
       </c>
       <c r="C311" t="s">
-        <v>164</v>
-      </c>
-      <c r="D311" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E311" t="s">
-        <v>7</v>
+        <v>57</v>
+      </c>
+      <c r="F311" t="s">
+        <v>84</v>
       </c>
       <c r="G311" t="s">
-        <v>18</v>
-      </c>
-      <c r="J311" t="s">
-        <v>129</v>
+        <v>17</v>
       </c>
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>257</v>
+        <v>194</v>
       </c>
       <c r="B312">
-        <v>4.1165589999999996</v>
+        <v>1</v>
       </c>
       <c r="C312" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D312" t="s">
         <v>4</v>
@@ -6087,64 +6111,64 @@
         <v>7</v>
       </c>
       <c r="G312" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J312" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="B313">
-        <v>6.3099999999999999E-10</v>
+        <v>4.1165589999999996</v>
       </c>
       <c r="C313" t="s">
         <v>165</v>
       </c>
       <c r="D313" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E313" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G313" t="s">
         <v>19</v>
       </c>
       <c r="J313" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="B314">
-        <v>0.110591844610756</v>
+        <v>6.3099999999999999E-10</v>
       </c>
       <c r="C314" t="s">
         <v>165</v>
       </c>
       <c r="D314" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E314" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G314" t="s">
         <v>19</v>
       </c>
       <c r="J314" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B315">
-        <v>0.58521199999999995</v>
+        <v>0.110591844610756</v>
       </c>
       <c r="C315" t="s">
         <v>165</v>
@@ -6159,21 +6183,21 @@
         <v>19</v>
       </c>
       <c r="J315" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B316">
-        <v>0.46507999999999999</v>
+        <v>0.58521199999999995</v>
       </c>
       <c r="C316" t="s">
         <v>165</v>
       </c>
       <c r="D316" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E316" t="s">
         <v>7</v>
@@ -6182,15 +6206,15 @@
         <v>19</v>
       </c>
       <c r="J316" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B317">
-        <v>0.18879541274411121</v>
+        <v>0.46507999999999999</v>
       </c>
       <c r="C317" t="s">
         <v>165</v>
@@ -6204,22 +6228,16 @@
       <c r="G317" t="s">
         <v>19</v>
       </c>
-      <c r="H317" t="s">
-        <v>136</v>
-      </c>
-      <c r="I317">
-        <v>0.20767495381477699</v>
-      </c>
       <c r="J317" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B318">
-        <v>1.0022394929271801</v>
+        <v>0.18879541274411121</v>
       </c>
       <c r="C318" t="s">
         <v>165</v>
@@ -6233,45 +6251,51 @@
       <c r="G318" t="s">
         <v>19</v>
       </c>
+      <c r="H318" t="s">
+        <v>136</v>
+      </c>
+      <c r="I318">
+        <v>0.20767495381477699</v>
+      </c>
       <c r="J318" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="B319">
-        <v>1.0481828925574601</v>
+        <v>1.0022394929271801</v>
       </c>
       <c r="C319" t="s">
         <v>165</v>
       </c>
       <c r="D319" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E319" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G319" t="s">
         <v>19</v>
       </c>
       <c r="J319" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B320">
-        <v>2.11713328049641</v>
+        <v>1.0481828925574601</v>
       </c>
       <c r="C320" t="s">
         <v>165</v>
       </c>
       <c r="D320" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E320" t="s">
         <v>24</v>
@@ -6280,61 +6304,61 @@
         <v>19</v>
       </c>
       <c r="J320" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="B321">
-        <v>-2.9967700185340698E-3</v>
+        <v>2.11713328049641</v>
       </c>
       <c r="C321" t="s">
         <v>165</v>
       </c>
       <c r="D321" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E321" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G321" t="s">
         <v>19</v>
       </c>
       <c r="J321" t="s">
-        <v>58</v>
+        <v>128</v>
       </c>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B322">
-        <v>1.9749609733914301E-4</v>
+        <v>-2.9967700185340698E-3</v>
       </c>
       <c r="C322" t="s">
         <v>165</v>
       </c>
       <c r="D322" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E322" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="G322" t="s">
         <v>19</v>
       </c>
       <c r="J322" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="B323">
-        <v>1.1155237898039301</v>
+        <v>1.9749609733914301E-4</v>
       </c>
       <c r="C323" t="s">
         <v>165</v>
@@ -6343,21 +6367,21 @@
         <v>4</v>
       </c>
       <c r="E323" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G323" t="s">
         <v>19</v>
       </c>
       <c r="J323" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="B324">
-        <v>-0.10135940306567701</v>
+        <v>1.1155237898039301</v>
       </c>
       <c r="C324" t="s">
         <v>165</v>
@@ -6366,13 +6390,13 @@
         <v>4</v>
       </c>
       <c r="E324" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G324" t="s">
         <v>19</v>
       </c>
       <c r="J324" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.25">
@@ -6380,7 +6404,7 @@
         <v>110</v>
       </c>
       <c r="B325">
-        <v>-1.4227000000000001</v>
+        <v>-0.10135940306567701</v>
       </c>
       <c r="C325" t="s">
         <v>165</v>
@@ -6398,134 +6422,134 @@
         <v>111</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A327" s="1" t="s">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>110</v>
+      </c>
+      <c r="B326">
+        <v>-1.4227000000000001</v>
+      </c>
+      <c r="C326" t="s">
+        <v>165</v>
+      </c>
+      <c r="D326" t="s">
+        <v>4</v>
+      </c>
+      <c r="E326" t="s">
+        <v>7</v>
+      </c>
+      <c r="G326" t="s">
+        <v>19</v>
+      </c>
+      <c r="J326" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A328" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B327" s="1" t="s">
+      <c r="B328" s="1" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A328" t="s">
-        <v>2</v>
-      </c>
-      <c r="B328" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B329" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B330" t="s">
-        <v>196</v>
+        <v>4</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B331" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
+        <v>6</v>
+      </c>
+      <c r="B332" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
         <v>216</v>
       </c>
-      <c r="B332" t="s">
+      <c r="B333" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A333" s="1" t="s">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>9</v>
-      </c>
-      <c r="B334" t="s">
-        <v>10</v>
-      </c>
-      <c r="C334" t="s">
-        <v>11</v>
-      </c>
-      <c r="D334" t="s">
-        <v>3</v>
-      </c>
-      <c r="E334" t="s">
-        <v>6</v>
-      </c>
-      <c r="F334" t="s">
-        <v>12</v>
-      </c>
-      <c r="G334" t="s">
-        <v>13</v>
-      </c>
-      <c r="H334" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>14</v>
-      </c>
-      <c r="B335">
-        <v>437.30238010762048</v>
+        <v>9</v>
+      </c>
+      <c r="B335" t="s">
+        <v>10</v>
       </c>
       <c r="C335" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D335" t="s">
+        <v>3</v>
       </c>
       <c r="E335" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F335" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G335" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H335" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>14</v>
+      </c>
+      <c r="B336">
+        <v>437.30238010762048</v>
+      </c>
+      <c r="C336" t="s">
+        <v>31</v>
+      </c>
+      <c r="E336" t="s">
+        <v>15</v>
+      </c>
+      <c r="F336" t="s">
+        <v>16</v>
+      </c>
+      <c r="G336" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
         <v>195</v>
       </c>
-      <c r="B336">
+      <c r="B337">
         <v>15.488183266908818</v>
-      </c>
-      <c r="C336" t="s">
-        <v>164</v>
-      </c>
-      <c r="D336" t="s">
-        <v>4</v>
-      </c>
-      <c r="E336" t="s">
-        <v>7</v>
-      </c>
-      <c r="G336" t="s">
-        <v>18</v>
-      </c>
-      <c r="H336" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A337" t="s">
-        <v>175</v>
-      </c>
-      <c r="B337">
-        <v>0.2742242079835131</v>
       </c>
       <c r="C337" t="s">
         <v>164</v>
@@ -6537,18 +6561,18 @@
         <v>7</v>
       </c>
       <c r="G337" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H337" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B338">
-        <v>13.162761983208627</v>
+        <v>0.2742242079835131</v>
       </c>
       <c r="C338" t="s">
         <v>164</v>
@@ -6563,21 +6587,21 @@
         <v>19</v>
       </c>
       <c r="H338" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>20</v>
+        <v>194</v>
       </c>
       <c r="B339">
-        <v>1.7769728677331647</v>
+        <v>13.162761983208627</v>
       </c>
       <c r="C339" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D339" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E339" t="s">
         <v>7</v>
@@ -6586,15 +6610,15 @@
         <v>19</v>
       </c>
       <c r="H339" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B340">
-        <v>0.2742242079835131</v>
+        <v>1.7769728677331647</v>
       </c>
       <c r="C340" t="s">
         <v>165</v>
@@ -6609,38 +6633,38 @@
         <v>19</v>
       </c>
       <c r="H340" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B341">
-        <v>2.2069564258513132</v>
+        <v>0.2742242079835131</v>
       </c>
       <c r="C341" t="s">
         <v>165</v>
       </c>
       <c r="D341" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E341" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G341" t="s">
         <v>19</v>
       </c>
       <c r="H341" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B342">
-        <v>69.49379695325851</v>
+        <v>2.2069564258513132</v>
       </c>
       <c r="C342" t="s">
         <v>165</v>
@@ -6649,13 +6673,13 @@
         <v>4</v>
       </c>
       <c r="E342" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G342" t="s">
         <v>19</v>
       </c>
       <c r="H342" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
@@ -6663,7 +6687,7 @@
         <v>25</v>
       </c>
       <c r="B343">
-        <v>51.979086409969391</v>
+        <v>69.49379695325851</v>
       </c>
       <c r="C343" t="s">
         <v>165</v>
@@ -6683,82 +6707,88 @@
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
+        <v>25</v>
+      </c>
+      <c r="B344">
+        <v>51.979086409969391</v>
+      </c>
+      <c r="C344" t="s">
+        <v>165</v>
+      </c>
+      <c r="D344" t="s">
+        <v>4</v>
+      </c>
+      <c r="E344" t="s">
+        <v>26</v>
+      </c>
+      <c r="G344" t="s">
+        <v>19</v>
+      </c>
+      <c r="H344" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
         <v>27</v>
       </c>
-      <c r="B344">
+      <c r="B345">
         <v>13.241738555107881</v>
       </c>
-      <c r="C344" t="s">
-        <v>165</v>
-      </c>
-      <c r="D344" t="s">
-        <v>4</v>
-      </c>
-      <c r="E344" t="s">
+      <c r="C345" t="s">
+        <v>165</v>
+      </c>
+      <c r="D345" t="s">
+        <v>4</v>
+      </c>
+      <c r="E345" t="s">
         <v>24</v>
       </c>
-      <c r="G344" t="s">
-        <v>19</v>
-      </c>
-      <c r="H344" t="s">
+      <c r="G345" t="s">
+        <v>19</v>
+      </c>
+      <c r="H345" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A347" s="1" t="s">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B347" s="1" t="s">
+      <c r="B348" s="1" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A348" t="s">
-        <v>2</v>
-      </c>
-      <c r="B348" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B349" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>3</v>
+      </c>
+      <c r="B350" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
         <v>5</v>
       </c>
-      <c r="B350" t="s">
+      <c r="B351" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="351" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>6</v>
-      </c>
-      <c r="B351" t="s">
-        <v>7</v>
-      </c>
-      <c r="C351"/>
-      <c r="D351"/>
-      <c r="E351"/>
-      <c r="F351"/>
-      <c r="G351"/>
-      <c r="H351"/>
-      <c r="I351"/>
-      <c r="J351"/>
-      <c r="K351"/>
     </row>
     <row r="352" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>216</v>
+        <v>6</v>
       </c>
       <c r="B352" t="s">
-        <v>220</v>
+        <v>7</v>
       </c>
       <c r="C352"/>
       <c r="D352"/>
@@ -6770,111 +6800,105 @@
       <c r="J352"/>
       <c r="K352"/>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A353" s="1" t="s">
+    <row r="353" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>216</v>
+      </c>
+      <c r="B353" t="s">
+        <v>220</v>
+      </c>
+      <c r="C353"/>
+      <c r="D353"/>
+      <c r="E353"/>
+      <c r="F353"/>
+      <c r="G353"/>
+      <c r="H353"/>
+      <c r="I353"/>
+      <c r="J353"/>
+      <c r="K353"/>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B353" s="1"/>
-      <c r="C353" s="1"/>
-      <c r="D353" s="1"/>
-      <c r="E353" s="1"/>
-      <c r="F353" s="1"/>
-      <c r="G353" s="1"/>
-      <c r="H353" s="1"/>
-      <c r="I353" s="1"/>
-      <c r="J353" s="1"/>
-      <c r="K353" s="1"/>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>9</v>
-      </c>
-      <c r="B354" t="s">
-        <v>10</v>
-      </c>
-      <c r="C354" t="s">
-        <v>11</v>
-      </c>
-      <c r="D354" t="s">
-        <v>3</v>
-      </c>
-      <c r="E354" t="s">
-        <v>6</v>
-      </c>
-      <c r="F354" t="s">
-        <v>12</v>
-      </c>
-      <c r="G354" t="s">
-        <v>13</v>
-      </c>
-      <c r="H354" t="s">
-        <v>44</v>
-      </c>
-      <c r="I354" t="s">
-        <v>45</v>
-      </c>
-      <c r="J354" t="s">
-        <v>5</v>
-      </c>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
+      <c r="E354" s="1"/>
+      <c r="F354" s="1"/>
+      <c r="G354" s="1"/>
+      <c r="H354" s="1"/>
+      <c r="I354" s="1"/>
+      <c r="J354" s="1"/>
+      <c r="K354" s="1"/>
     </row>
     <row r="355" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>14</v>
-      </c>
-      <c r="B355">
-        <v>27.36</v>
+        <v>9</v>
+      </c>
+      <c r="B355" t="s">
+        <v>10</v>
       </c>
       <c r="C355" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D355" t="s">
+        <v>3</v>
       </c>
       <c r="E355" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F355" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G355" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H355" t="s">
-        <v>156</v>
-      </c>
-      <c r="I355">
-        <v>1</v>
+        <v>44</v>
+      </c>
+      <c r="I355" t="s">
+        <v>45</v>
+      </c>
+      <c r="J355" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="B356">
-        <v>2.2000000000000002</v>
+        <v>27.36</v>
       </c>
       <c r="C356" t="s">
-        <v>164</v>
-      </c>
-      <c r="D356" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E356" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="F356" t="s">
+        <v>16</v>
       </c>
       <c r="G356" t="s">
-        <v>18</v>
-      </c>
-      <c r="J356" t="s">
-        <v>46</v>
+        <v>17</v>
+      </c>
+      <c r="H356" t="s">
+        <v>156</v>
+      </c>
+      <c r="I356">
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="B357">
-        <v>1.1000000000000001</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="C357" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D357" t="s">
         <v>4</v>
@@ -6883,24 +6907,24 @@
         <v>7</v>
       </c>
       <c r="G357" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J357" t="s">
-        <v>143</v>
+        <v>46</v>
       </c>
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B358">
-        <v>2.2000000000000002</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C358" t="s">
         <v>165</v>
       </c>
       <c r="D358" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E358" t="s">
         <v>7</v>
@@ -6909,197 +6933,200 @@
         <v>19</v>
       </c>
       <c r="J358" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="B359">
-        <v>-1.2999999999999999E-3</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="C359" t="s">
         <v>165</v>
       </c>
       <c r="D359" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E359" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="G359" t="s">
         <v>19</v>
       </c>
       <c r="J359" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="B360">
-        <v>7.6</v>
+        <v>-1.2999999999999999E-3</v>
       </c>
       <c r="C360" t="s">
         <v>165</v>
       </c>
       <c r="D360" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E360" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="G360" t="s">
         <v>19</v>
       </c>
       <c r="J360" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>25</v>
+      </c>
+      <c r="B361">
+        <v>7.6</v>
+      </c>
+      <c r="C361" t="s">
+        <v>165</v>
+      </c>
+      <c r="D361" t="s">
+        <v>4</v>
+      </c>
+      <c r="E361" t="s">
+        <v>26</v>
+      </c>
+      <c r="G361" t="s">
+        <v>19</v>
+      </c>
+      <c r="J361" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
         <v>159</v>
       </c>
-      <c r="B361">
+      <c r="B362">
         <v>0.22</v>
       </c>
-      <c r="C361" t="s">
-        <v>165</v>
-      </c>
-      <c r="D361" t="s">
-        <v>4</v>
-      </c>
-      <c r="E361" t="s">
-        <v>7</v>
-      </c>
-      <c r="G361" t="s">
-        <v>19</v>
-      </c>
-      <c r="J361" t="s">
+      <c r="C362" t="s">
+        <v>165</v>
+      </c>
+      <c r="D362" t="s">
+        <v>4</v>
+      </c>
+      <c r="E362" t="s">
+        <v>7</v>
+      </c>
+      <c r="G362" t="s">
+        <v>19</v>
+      </c>
+      <c r="J362" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A363" s="1" t="s">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B363" s="1" t="s">
+      <c r="B364" s="1" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A364" t="s">
-        <v>2</v>
-      </c>
-      <c r="B364" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>227</v>
+        <v>2</v>
       </c>
       <c r="B365" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="366" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>3</v>
+        <v>227</v>
       </c>
       <c r="B366" t="s">
-        <v>4</v>
+        <v>228</v>
       </c>
     </row>
     <row r="367" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B367" t="s">
-        <v>198</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
+        <v>5</v>
+      </c>
+      <c r="B368" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
         <v>6</v>
       </c>
-      <c r="B368" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
+      <c r="B369" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
         <v>216</v>
       </c>
-      <c r="B369" t="s">
+      <c r="B370" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A370" s="1" t="s">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A371" t="s">
-        <v>9</v>
-      </c>
-      <c r="B371" t="s">
-        <v>10</v>
-      </c>
-      <c r="C371" t="s">
-        <v>11</v>
-      </c>
-      <c r="D371" t="s">
-        <v>3</v>
-      </c>
-      <c r="E371" t="s">
-        <v>6</v>
-      </c>
-      <c r="F371" t="s">
-        <v>12</v>
-      </c>
-      <c r="G371" t="s">
-        <v>13</v>
-      </c>
-      <c r="H371" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>14</v>
-      </c>
-      <c r="B372">
-        <v>1.95</v>
+        <v>9</v>
+      </c>
+      <c r="B372" t="s">
+        <v>10</v>
       </c>
       <c r="C372" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D372" t="s">
+        <v>3</v>
       </c>
       <c r="E372" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F372" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G372" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="H372" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="B373">
-        <v>0.26300000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="C373" t="s">
         <v>31</v>
       </c>
       <c r="E373" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F373" t="s">
         <v>16</v>
@@ -7110,36 +7137,33 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="B374">
-        <v>1</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="C374" t="s">
-        <v>164</v>
-      </c>
-      <c r="D374" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E374" t="s">
         <v>7</v>
       </c>
+      <c r="F374" t="s">
+        <v>16</v>
+      </c>
       <c r="G374" t="s">
-        <v>18</v>
-      </c>
-      <c r="H374" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="B375">
-        <v>1.25E-3</v>
+        <v>1</v>
       </c>
       <c r="C375" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D375" t="s">
         <v>4</v>
@@ -7148,18 +7172,18 @@
         <v>7</v>
       </c>
       <c r="G375" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H375" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>141</v>
+        <v>257</v>
       </c>
       <c r="B376">
-        <v>4.0000000000000001E-10</v>
+        <v>1.25E-3</v>
       </c>
       <c r="C376" t="s">
         <v>165</v>
@@ -7168,21 +7192,21 @@
         <v>4</v>
       </c>
       <c r="E376" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G376" t="s">
         <v>19</v>
       </c>
       <c r="H376" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B377">
-        <v>4.04</v>
+        <v>4.0000000000000001E-10</v>
       </c>
       <c r="C377" t="s">
         <v>165</v>
@@ -7191,21 +7215,21 @@
         <v>4</v>
       </c>
       <c r="E377" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G377" t="s">
         <v>19</v>
       </c>
       <c r="H377" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B378">
-        <v>7.44</v>
+        <v>4.04</v>
       </c>
       <c r="C378" t="s">
         <v>165</v>
@@ -7220,21 +7244,21 @@
         <v>19</v>
       </c>
       <c r="H378" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B379">
-        <v>-8.6</v>
+        <v>7.44</v>
       </c>
       <c r="C379" t="s">
         <v>165</v>
       </c>
       <c r="D379" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E379" t="s">
         <v>7</v>
@@ -7243,21 +7267,21 @@
         <v>19</v>
       </c>
       <c r="H379" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B380">
-        <v>1.98</v>
+        <v>-8.6</v>
       </c>
       <c r="C380" t="s">
         <v>165</v>
       </c>
       <c r="D380" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="E380" t="s">
         <v>7</v>
@@ -7266,15 +7290,15 @@
         <v>19</v>
       </c>
       <c r="H380" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="B381">
-        <v>0.31900000000000001</v>
+        <v>1.98</v>
       </c>
       <c r="C381" t="s">
         <v>165</v>
@@ -7289,247 +7313,250 @@
         <v>19</v>
       </c>
       <c r="H381" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="B382">
-        <v>1.3779999999999999</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="C382" t="s">
         <v>165</v>
       </c>
       <c r="D382" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E382" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G382" t="s">
         <v>19</v>
       </c>
       <c r="H382" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B383">
-        <v>-3.6099999999999999E-3</v>
+        <v>1.3779999999999999</v>
       </c>
       <c r="C383" t="s">
         <v>165</v>
       </c>
       <c r="D383" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E383" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G383" t="s">
         <v>19</v>
       </c>
       <c r="H383" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
+        <v>55</v>
+      </c>
+      <c r="B384">
+        <v>-3.6099999999999999E-3</v>
+      </c>
+      <c r="C384" t="s">
+        <v>165</v>
+      </c>
+      <c r="D384" t="s">
+        <v>56</v>
+      </c>
+      <c r="E384" t="s">
+        <v>57</v>
+      </c>
+      <c r="G384" t="s">
+        <v>19</v>
+      </c>
+      <c r="H384" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
         <v>25</v>
       </c>
-      <c r="B384">
+      <c r="B385">
         <v>0.54100000000000004</v>
       </c>
-      <c r="C384" t="s">
-        <v>165</v>
-      </c>
-      <c r="D384" t="s">
-        <v>4</v>
-      </c>
-      <c r="E384" t="s">
+      <c r="C385" t="s">
+        <v>165</v>
+      </c>
+      <c r="D385" t="s">
+        <v>4</v>
+      </c>
+      <c r="E385" t="s">
         <v>26</v>
       </c>
-      <c r="G384" t="s">
-        <v>19</v>
-      </c>
-      <c r="H384" t="s">
+      <c r="G385" t="s">
+        <v>19</v>
+      </c>
+      <c r="H385" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A385" t="s">
-        <v>27</v>
-      </c>
-      <c r="B385">
-        <v>8.2669999999999995</v>
-      </c>
-      <c r="C385" t="s">
-        <v>165</v>
-      </c>
-      <c r="D385" t="s">
-        <v>4</v>
-      </c>
-      <c r="E385" t="s">
-        <v>24</v>
-      </c>
-      <c r="G385" t="s">
-        <v>19</v>
-      </c>
-      <c r="H385" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
+        <v>27</v>
+      </c>
+      <c r="B386">
+        <v>8.2669999999999995</v>
+      </c>
+      <c r="C386" t="s">
+        <v>165</v>
+      </c>
+      <c r="D386" t="s">
+        <v>4</v>
+      </c>
+      <c r="E386" t="s">
+        <v>24</v>
+      </c>
+      <c r="G386" t="s">
+        <v>19</v>
+      </c>
+      <c r="H386" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
         <v>150</v>
       </c>
-      <c r="B386">
+      <c r="B387">
         <v>-4.24E-2</v>
       </c>
-      <c r="C386" t="s">
-        <v>165</v>
-      </c>
-      <c r="D386" t="s">
+      <c r="C387" t="s">
+        <v>165</v>
+      </c>
+      <c r="D387" t="s">
         <v>21</v>
       </c>
-      <c r="E386" t="s">
-        <v>7</v>
-      </c>
-      <c r="G386" t="s">
-        <v>19</v>
-      </c>
-      <c r="H386" t="s">
+      <c r="E387" t="s">
+        <v>7</v>
+      </c>
+      <c r="G387" t="s">
+        <v>19</v>
+      </c>
+      <c r="H387" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A388" s="1" t="s">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A389" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B388" s="1" t="s">
+      <c r="B389" s="1" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A389" t="s">
-        <v>2</v>
-      </c>
-      <c r="B389" s="11" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="390" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>227</v>
-      </c>
-      <c r="B390" t="s">
-        <v>229</v>
+        <v>2</v>
+      </c>
+      <c r="B390" s="11" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>3</v>
+        <v>227</v>
       </c>
       <c r="B391" t="s">
-        <v>4</v>
+        <v>229</v>
       </c>
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B392" t="s">
-        <v>260</v>
+        <v>4</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B393" t="s">
-        <v>7</v>
+        <v>260</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
+        <v>6</v>
+      </c>
+      <c r="B394" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
         <v>216</v>
       </c>
-      <c r="B394" t="s">
+      <c r="B395" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="395" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A395" s="1" t="s">
+    <row r="396" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A396" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A396" t="s">
-        <v>9</v>
-      </c>
-      <c r="B396" t="s">
-        <v>10</v>
-      </c>
-      <c r="C396" t="s">
-        <v>11</v>
-      </c>
-      <c r="D396" t="s">
-        <v>3</v>
-      </c>
-      <c r="E396" t="s">
-        <v>6</v>
-      </c>
-      <c r="F396" t="s">
-        <v>12</v>
-      </c>
-      <c r="G396" t="s">
-        <v>13</v>
-      </c>
-      <c r="H396" t="s">
-        <v>5</v>
-      </c>
-      <c r="I396" t="s">
-        <v>2</v>
-      </c>
-      <c r="K396" s="12"/>
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>69</v>
-      </c>
-      <c r="B397">
-        <v>0.371</v>
+        <v>9</v>
+      </c>
+      <c r="B397" t="s">
+        <v>10</v>
       </c>
       <c r="C397" t="s">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="D397" t="s">
+        <v>3</v>
       </c>
       <c r="E397" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F397" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G397" t="s">
-        <v>17</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="H397" t="s">
+        <v>5</v>
+      </c>
+      <c r="I397" t="s">
+        <v>2</v>
+      </c>
+      <c r="K397" s="12"/>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="B398">
-        <v>2.29</v>
+        <v>0.371</v>
       </c>
       <c r="C398" t="s">
         <v>31</v>
       </c>
       <c r="E398" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F398" t="s">
         <v>16</v>
@@ -7540,30 +7567,27 @@
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>259</v>
-      </c>
-      <c r="B399" s="12">
-        <v>3.9999999999999998E-7</v>
+        <v>14</v>
+      </c>
+      <c r="B399">
+        <v>2.29</v>
       </c>
       <c r="C399" t="s">
         <v>31</v>
       </c>
       <c r="E399" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F399" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="G399" t="s">
         <v>17</v>
       </c>
-      <c r="I399" t="s">
-        <v>263</v>
-      </c>
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="B400" s="12">
         <v>3.9999999999999998E-7</v>
@@ -7581,15 +7605,15 @@
         <v>17</v>
       </c>
       <c r="I400" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>151</v>
-      </c>
-      <c r="B401">
-        <v>0.19400000000000001</v>
+        <v>167</v>
+      </c>
+      <c r="B401" s="12">
+        <v>3.9999999999999998E-7</v>
       </c>
       <c r="C401" t="s">
         <v>31</v>
@@ -7598,18 +7622,21 @@
         <v>7</v>
       </c>
       <c r="F401" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G401" t="s">
         <v>17</v>
       </c>
+      <c r="I401" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B402">
-        <v>0.80900000000000005</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="C402" t="s">
         <v>31</v>
@@ -7626,56 +7653,53 @@
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="B403">
-        <v>1</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="C403" t="s">
-        <v>164</v>
-      </c>
-      <c r="D403" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E403" t="s">
         <v>7</v>
       </c>
+      <c r="F403" t="s">
+        <v>84</v>
+      </c>
       <c r="G403" t="s">
-        <v>18</v>
-      </c>
-      <c r="H403" t="s">
-        <v>260</v>
+        <v>17</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="B404">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="C404" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D404" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E404" t="s">
         <v>7</v>
       </c>
       <c r="G404" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H404" t="s">
-        <v>154</v>
+        <v>260</v>
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="B405">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="C405" t="s">
         <v>165</v>
@@ -7690,38 +7714,38 @@
         <v>19</v>
       </c>
       <c r="H405" t="s">
-        <v>102</v>
+        <v>154</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="B406">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="C406" t="s">
         <v>165</v>
       </c>
       <c r="D406" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E406" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G406" t="s">
         <v>19</v>
       </c>
       <c r="H406" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="B407">
-        <v>1.12E-2</v>
+        <v>1.63</v>
       </c>
       <c r="C407" t="s">
         <v>165</v>
@@ -7730,21 +7754,21 @@
         <v>4</v>
       </c>
       <c r="E407" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G407" t="s">
         <v>19</v>
       </c>
       <c r="H407" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="B408">
-        <v>2.62</v>
+        <v>1.12E-2</v>
       </c>
       <c r="C408" t="s">
         <v>165</v>
@@ -7753,21 +7777,21 @@
         <v>4</v>
       </c>
       <c r="E408" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G408" t="s">
         <v>19</v>
       </c>
       <c r="H408" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="B409">
-        <v>0.27200000000000002</v>
+        <v>2.62</v>
       </c>
       <c r="C409" t="s">
         <v>165</v>
@@ -7776,45 +7800,44 @@
         <v>4</v>
       </c>
       <c r="E409" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G409" t="s">
         <v>19</v>
       </c>
       <c r="H409" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="B410">
-        <v>7.98</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="C410" t="s">
         <v>165</v>
       </c>
       <c r="D410" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E410" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G410" t="s">
         <v>19</v>
       </c>
       <c r="H410" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="B411">
-        <f>-B410/1000</f>
-        <v>-7.980000000000001E-3</v>
+        <v>7.98</v>
       </c>
       <c r="C411" t="s">
         <v>165</v>
@@ -7823,123 +7846,124 @@
         <v>56</v>
       </c>
       <c r="E411" t="s">
+        <v>7</v>
+      </c>
+      <c r="G411" t="s">
+        <v>19</v>
+      </c>
+      <c r="H411" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>55</v>
+      </c>
+      <c r="B412">
+        <f>-B411/1000</f>
+        <v>-7.980000000000001E-3</v>
+      </c>
+      <c r="C412" t="s">
+        <v>165</v>
+      </c>
+      <c r="D412" t="s">
+        <v>56</v>
+      </c>
+      <c r="E412" t="s">
         <v>57</v>
       </c>
-      <c r="G411" t="s">
-        <v>19</v>
-      </c>
-      <c r="H411" t="s">
+      <c r="G412" t="s">
+        <v>19</v>
+      </c>
+      <c r="H412" t="s">
         <v>58</v>
       </c>
-      <c r="I411" t="s">
+      <c r="I412" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A413" s="1" t="s">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B413" s="1" t="s">
+      <c r="B414" s="1" t="s">
         <v>201</v>
-      </c>
-    </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
-        <v>2</v>
-      </c>
-      <c r="B414" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B415" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
+        <v>3</v>
+      </c>
+      <c r="B416" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
         <v>5</v>
       </c>
-      <c r="B416" t="s">
+      <c r="B417" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A417" t="s">
-        <v>6</v>
-      </c>
-      <c r="B417" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
+        <v>6</v>
+      </c>
+      <c r="B418" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
         <v>216</v>
       </c>
-      <c r="B418" t="s">
+      <c r="B419" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="419" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A419" s="1" t="s">
+    <row r="420" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A420" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>9</v>
-      </c>
-      <c r="B420" t="s">
-        <v>10</v>
-      </c>
-      <c r="C420" t="s">
-        <v>11</v>
-      </c>
-      <c r="D420" t="s">
-        <v>3</v>
-      </c>
-      <c r="E420" t="s">
-        <v>6</v>
-      </c>
-      <c r="F420" t="s">
-        <v>13</v>
-      </c>
-      <c r="G420" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>201</v>
-      </c>
-      <c r="B421">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B421" t="s">
+        <v>10</v>
       </c>
       <c r="C421" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="D421" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E421" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F421" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G421" t="s">
-        <v>202</v>
+        <v>5</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B422">
-        <v>0.13180285392336399</v>
+        <v>1</v>
       </c>
       <c r="C422" t="s">
         <v>164</v>
@@ -7951,24 +7975,24 @@
         <v>7</v>
       </c>
       <c r="F422" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G422" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>87</v>
+        <v>197</v>
       </c>
       <c r="B423">
-        <v>0.38852820840736102</v>
+        <v>0.13180285392336399</v>
       </c>
       <c r="C423" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D423" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E423" t="s">
         <v>7</v>
@@ -7977,15 +8001,15 @@
         <v>19</v>
       </c>
       <c r="G423" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B424">
-        <v>0.47966893766927499</v>
+        <v>0.38852820840736102</v>
       </c>
       <c r="C424" t="s">
         <v>165</v>
@@ -8000,38 +8024,38 @@
         <v>19</v>
       </c>
       <c r="G424" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="B425">
-        <v>0.1</v>
+        <v>0.47966893766927499</v>
       </c>
       <c r="C425" t="s">
         <v>165</v>
       </c>
       <c r="D425" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E425" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F425" t="s">
         <v>19</v>
       </c>
       <c r="G425" t="s">
-        <v>33</v>
+        <v>162</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B426">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="C426" t="s">
         <v>165</v>
@@ -8046,271 +8070,270 @@
         <v>19</v>
       </c>
       <c r="G426" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>27</v>
+      </c>
+      <c r="B427">
+        <v>0.6</v>
+      </c>
+      <c r="C427" t="s">
+        <v>165</v>
+      </c>
+      <c r="D427" t="s">
+        <v>4</v>
+      </c>
+      <c r="E427" t="s">
+        <v>24</v>
+      </c>
+      <c r="F427" t="s">
+        <v>19</v>
+      </c>
+      <c r="G427" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A428" s="1" t="s">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A429" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B428" s="1" t="s">
+      <c r="B429" s="1" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
-        <v>3</v>
-      </c>
-      <c r="B429" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B430" t="s">
-        <v>226</v>
+        <v>4</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B431" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
+        <v>13</v>
+      </c>
+      <c r="B432" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
         <v>2</v>
       </c>
-      <c r="B432" t="s">
+      <c r="B433" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A433" t="s">
-        <v>6</v>
-      </c>
-      <c r="B433" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
+        <v>6</v>
+      </c>
+      <c r="B434" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
         <v>216</v>
       </c>
-      <c r="B434" t="s">
+      <c r="B435" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A435" s="1" t="s">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A436" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B435" s="1"/>
-      <c r="C435" s="1"/>
-      <c r="D435" s="1"/>
-      <c r="E435" s="1"/>
-      <c r="F435" s="1"/>
-      <c r="G435" s="1"/>
-      <c r="H435" s="1"/>
-      <c r="I435" s="1"/>
-      <c r="J435" s="1"/>
-      <c r="K435" s="1"/>
-    </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A436" t="s">
-        <v>9</v>
-      </c>
-      <c r="B436" t="s">
-        <v>10</v>
-      </c>
-      <c r="C436" t="s">
-        <v>11</v>
-      </c>
-      <c r="D436" t="s">
-        <v>3</v>
-      </c>
-      <c r="E436" t="s">
-        <v>6</v>
-      </c>
-      <c r="F436" t="s">
-        <v>13</v>
-      </c>
-      <c r="G436" t="s">
-        <v>5</v>
-      </c>
+      <c r="B436" s="1"/>
+      <c r="C436" s="1"/>
+      <c r="D436" s="1"/>
+      <c r="E436" s="1"/>
+      <c r="F436" s="1"/>
+      <c r="G436" s="1"/>
+      <c r="H436" s="1"/>
+      <c r="I436" s="1"/>
+      <c r="J436" s="1"/>
+      <c r="K436" s="1"/>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>203</v>
-      </c>
-      <c r="B437">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B437" t="s">
+        <v>10</v>
       </c>
       <c r="C437" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="D437" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E437" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F437" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G437" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
+        <v>203</v>
+      </c>
+      <c r="B438">
+        <v>1</v>
+      </c>
+      <c r="C438" t="s">
+        <v>164</v>
+      </c>
+      <c r="D438" t="s">
+        <v>4</v>
+      </c>
+      <c r="E438" t="s">
+        <v>7</v>
+      </c>
+      <c r="F438" t="s">
+        <v>18</v>
+      </c>
+      <c r="G438" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
         <v>169</v>
       </c>
-      <c r="B438">
+      <c r="B439">
         <f>(1/0.0562)*0.0085612534146254</f>
         <v>0.1523354700111281</v>
       </c>
-      <c r="C438" t="s">
+      <c r="C439" t="s">
         <v>164</v>
       </c>
-      <c r="D438" t="s">
-        <v>4</v>
-      </c>
-      <c r="E438" t="s">
-        <v>7</v>
-      </c>
-      <c r="F438" t="s">
-        <v>19</v>
-      </c>
-      <c r="G438" t="s">
+      <c r="D439" t="s">
+        <v>4</v>
+      </c>
+      <c r="E439" t="s">
+        <v>7</v>
+      </c>
+      <c r="F439" t="s">
+        <v>19</v>
+      </c>
+      <c r="G439" t="s">
         <v>168</v>
       </c>
-      <c r="H438" t="s">
+      <c r="H439" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A439" t="s">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
         <v>183</v>
       </c>
-      <c r="B439">
+      <c r="B440">
         <f>(1/0.0562)*0.0165620491137194</f>
         <v>0.29469838280639504</v>
       </c>
-      <c r="C439" t="s">
+      <c r="C440" t="s">
         <v>164</v>
       </c>
-      <c r="D439" t="s">
-        <v>4</v>
-      </c>
-      <c r="E439" t="s">
-        <v>7</v>
-      </c>
-      <c r="F439" t="s">
-        <v>19</v>
-      </c>
-      <c r="G439" t="s">
+      <c r="D440" t="s">
+        <v>4</v>
+      </c>
+      <c r="E440" t="s">
+        <v>7</v>
+      </c>
+      <c r="F440" t="s">
+        <v>19</v>
+      </c>
+      <c r="G440" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A440" t="s">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
         <v>185</v>
       </c>
-      <c r="B440">
+      <c r="B441">
         <f>(1/0.0562)*0.0209977698868578</f>
         <v>0.37362579869853735</v>
       </c>
-      <c r="C440" t="s">
+      <c r="C441" t="s">
         <v>164</v>
       </c>
-      <c r="D440" t="s">
-        <v>4</v>
-      </c>
-      <c r="E440" t="s">
-        <v>7</v>
-      </c>
-      <c r="F440" t="s">
-        <v>19</v>
-      </c>
-      <c r="G440" t="s">
+      <c r="D441" t="s">
+        <v>4</v>
+      </c>
+      <c r="E441" t="s">
+        <v>7</v>
+      </c>
+      <c r="F441" t="s">
+        <v>19</v>
+      </c>
+      <c r="G441" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A441" t="s">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
         <v>201</v>
       </c>
-      <c r="B441">
+      <c r="B442">
         <f>(1/0.0562)*0.00925252694737966</f>
         <v>0.16463571080746725</v>
       </c>
-      <c r="C441" t="s">
+      <c r="C442" t="s">
         <v>164</v>
       </c>
-      <c r="D441" t="s">
-        <v>4</v>
-      </c>
-      <c r="E441" t="s">
-        <v>7</v>
-      </c>
-      <c r="F441" t="s">
-        <v>19</v>
-      </c>
-      <c r="G441" t="s">
+      <c r="D442" t="s">
+        <v>4</v>
+      </c>
+      <c r="E442" t="s">
+        <v>7</v>
+      </c>
+      <c r="F442" t="s">
+        <v>19</v>
+      </c>
+      <c r="G442" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A442" t="s">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
         <v>86</v>
       </c>
-      <c r="B442">
+      <c r="B443">
         <f>(1/0.0562)*0.000803030859695695</f>
         <v>1.4288805332663612E-2</v>
       </c>
-      <c r="C442" t="s">
-        <v>165</v>
-      </c>
-      <c r="D442" t="s">
+      <c r="C443" t="s">
+        <v>165</v>
+      </c>
+      <c r="D443" t="s">
         <v>21</v>
       </c>
-      <c r="E442" t="s">
-        <v>7</v>
-      </c>
-      <c r="F442" t="s">
-        <v>19</v>
-      </c>
-      <c r="G442" t="s">
+      <c r="E443" t="s">
+        <v>7</v>
+      </c>
+      <c r="F443" t="s">
+        <v>19</v>
+      </c>
+      <c r="G443" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A443" t="s">
-        <v>25</v>
-      </c>
-      <c r="B443">
-        <f>(1/0.0562)*0.103774876494967</f>
-        <v>1.8465280515118683</v>
-      </c>
-      <c r="C443" t="s">
-        <v>165</v>
-      </c>
-      <c r="D443" t="s">
-        <v>4</v>
-      </c>
-      <c r="E443" t="s">
-        <v>26</v>
-      </c>
-      <c r="F443" t="s">
-        <v>19</v>
-      </c>
-      <c r="G443" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.25">
@@ -8318,281 +8341,281 @@
         <v>25</v>
       </c>
       <c r="B444">
+        <f>(1/0.0562)*0.103774876494967</f>
+        <v>1.8465280515118683</v>
+      </c>
+      <c r="C444" t="s">
+        <v>165</v>
+      </c>
+      <c r="D444" t="s">
+        <v>4</v>
+      </c>
+      <c r="E444" t="s">
+        <v>26</v>
+      </c>
+      <c r="F444" t="s">
+        <v>19</v>
+      </c>
+      <c r="G444" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>25</v>
+      </c>
+      <c r="B445">
         <f>(1/0.0562)*0.133972324705964</f>
         <v>2.3838491940562991</v>
       </c>
-      <c r="C444" t="s">
-        <v>165</v>
-      </c>
-      <c r="D444" t="s">
-        <v>4</v>
-      </c>
-      <c r="E444" t="s">
+      <c r="C445" t="s">
+        <v>165</v>
+      </c>
+      <c r="D445" t="s">
+        <v>4</v>
+      </c>
+      <c r="E445" t="s">
         <v>26</v>
       </c>
-      <c r="F444" t="s">
-        <v>19</v>
-      </c>
-      <c r="G444" t="s">
+      <c r="F445" t="s">
+        <v>19</v>
+      </c>
+      <c r="G445" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A446" s="1" t="s">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A447" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B446" s="1" t="s">
+      <c r="B447" s="1" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
-        <v>3</v>
-      </c>
-      <c r="B447" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B448" t="s">
-        <v>226</v>
+        <v>4</v>
       </c>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B449" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B450" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B451" t="s">
-        <v>7</v>
+        <v>224</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
+        <v>6</v>
+      </c>
+      <c r="B452" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
         <v>216</v>
       </c>
-      <c r="B452" t="s">
+      <c r="B453" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A453" s="1" t="s">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A454" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A454" t="s">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
         <v>9</v>
       </c>
-      <c r="B454" t="s">
+      <c r="B455" t="s">
         <v>10</v>
       </c>
-      <c r="C454" t="s">
+      <c r="C455" t="s">
         <v>11</v>
       </c>
-      <c r="D454" t="s">
+      <c r="D455" t="s">
         <v>3</v>
       </c>
-      <c r="E454" t="s">
+      <c r="E455" t="s">
         <v>6</v>
       </c>
-      <c r="F454" t="s">
+      <c r="F455" t="s">
         <v>13</v>
       </c>
-      <c r="G454" t="s">
+      <c r="G455" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="455" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A455" t="s">
+    <row r="456" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
         <v>204</v>
       </c>
-      <c r="B455">
+      <c r="B456">
         <v>1</v>
       </c>
-      <c r="C455" t="s">
+      <c r="C456" t="s">
         <v>164</v>
       </c>
-      <c r="D455" t="s">
-        <v>4</v>
-      </c>
-      <c r="E455" t="s">
-        <v>7</v>
-      </c>
-      <c r="F455" t="s">
+      <c r="D456" t="s">
+        <v>4</v>
+      </c>
+      <c r="E456" t="s">
+        <v>7</v>
+      </c>
+      <c r="F456" t="s">
         <v>18</v>
       </c>
-      <c r="G455" t="s">
+      <c r="G456" t="s">
         <v>226</v>
       </c>
-      <c r="H455"/>
-      <c r="I455"/>
-      <c r="J455"/>
-      <c r="K455"/>
-    </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
+      <c r="H456"/>
+      <c r="I456"/>
+      <c r="J456"/>
+      <c r="K456"/>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
         <v>169</v>
       </c>
-      <c r="B456">
+      <c r="B457">
         <f>(1/0.053177)*0.0085612534146254</f>
         <v>0.1609954193471877</v>
       </c>
-      <c r="C456" t="s">
+      <c r="C457" t="s">
         <v>164</v>
       </c>
-      <c r="D456" t="s">
-        <v>4</v>
-      </c>
-      <c r="E456" t="s">
-        <v>7</v>
-      </c>
-      <c r="F456" t="s">
-        <v>19</v>
-      </c>
-      <c r="G456" t="s">
+      <c r="D457" t="s">
+        <v>4</v>
+      </c>
+      <c r="E457" t="s">
+        <v>7</v>
+      </c>
+      <c r="F457" t="s">
+        <v>19</v>
+      </c>
+      <c r="G457" t="s">
         <v>168</v>
       </c>
-      <c r="H456" t="s">
+      <c r="H457" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A457" t="s">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
         <v>172</v>
       </c>
-      <c r="B457">
+      <c r="B458">
         <f>(1/0.053177)*0.0130181682473286</f>
         <v>0.24480824881675539</v>
       </c>
-      <c r="C457" t="s">
+      <c r="C458" t="s">
         <v>164</v>
       </c>
-      <c r="D457" t="s">
-        <v>4</v>
-      </c>
-      <c r="E457" t="s">
-        <v>7</v>
-      </c>
-      <c r="F457" t="s">
-        <v>19</v>
-      </c>
-      <c r="G457" t="s">
+      <c r="D458" t="s">
+        <v>4</v>
+      </c>
+      <c r="E458" t="s">
+        <v>7</v>
+      </c>
+      <c r="F458" t="s">
+        <v>19</v>
+      </c>
+      <c r="G458" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A458" t="s">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
         <v>188</v>
       </c>
-      <c r="B458">
+      <c r="B459">
         <f>(1/0.053177)*0.0216120622410464</f>
         <v>0.40641747825274838</v>
       </c>
-      <c r="C458" t="s">
+      <c r="C459" t="s">
         <v>164</v>
       </c>
-      <c r="D458" t="s">
-        <v>4</v>
-      </c>
-      <c r="E458" t="s">
-        <v>7</v>
-      </c>
-      <c r="F458" t="s">
-        <v>19</v>
-      </c>
-      <c r="G458" t="s">
+      <c r="D459" t="s">
+        <v>4</v>
+      </c>
+      <c r="E459" t="s">
+        <v>7</v>
+      </c>
+      <c r="F459" t="s">
+        <v>19</v>
+      </c>
+      <c r="G459" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A459" t="s">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
         <v>201</v>
       </c>
-      <c r="B459">
+      <c r="B460">
         <f>(1/0.053177)*0.00934397682507009</f>
         <v>0.17571462897625084</v>
       </c>
-      <c r="C459" t="s">
+      <c r="C460" t="s">
         <v>164</v>
       </c>
-      <c r="D459" t="s">
-        <v>4</v>
-      </c>
-      <c r="E459" t="s">
-        <v>7</v>
-      </c>
-      <c r="F459" t="s">
-        <v>19</v>
-      </c>
-      <c r="G459" t="s">
+      <c r="D460" t="s">
+        <v>4</v>
+      </c>
+      <c r="E460" t="s">
+        <v>7</v>
+      </c>
+      <c r="F460" t="s">
+        <v>19</v>
+      </c>
+      <c r="G460" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A460" t="s">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
         <v>86</v>
       </c>
-      <c r="B460">
+      <c r="B461">
         <f>(1/0.053177)*0.000642010008010976</f>
         <v>1.2073076856742127E-2</v>
       </c>
-      <c r="C460" t="s">
-        <v>165</v>
-      </c>
-      <c r="D460" t="s">
+      <c r="C461" t="s">
+        <v>165</v>
+      </c>
+      <c r="D461" t="s">
         <v>21</v>
       </c>
-      <c r="E460" t="s">
-        <v>7</v>
-      </c>
-      <c r="F460" t="s">
-        <v>19</v>
-      </c>
-      <c r="G460" t="s">
+      <c r="E461" t="s">
+        <v>7</v>
+      </c>
+      <c r="F461" t="s">
+        <v>19</v>
+      </c>
+      <c r="G461" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A461" t="s">
-        <v>25</v>
-      </c>
-      <c r="B461">
-        <f>(1/0.053177)*0.104800563836034</f>
-        <v>1.9707874426168082</v>
-      </c>
-      <c r="C461" t="s">
-        <v>165</v>
-      </c>
-      <c r="D461" t="s">
-        <v>4</v>
-      </c>
-      <c r="E461" t="s">
-        <v>26</v>
-      </c>
-      <c r="F461" t="s">
-        <v>19</v>
-      </c>
-      <c r="G461" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.25">
@@ -8600,302 +8623,299 @@
         <v>25</v>
       </c>
       <c r="B462">
+        <f>(1/0.053177)*0.104800563836034</f>
+        <v>1.9707874426168082</v>
+      </c>
+      <c r="C462" t="s">
+        <v>165</v>
+      </c>
+      <c r="D462" t="s">
+        <v>4</v>
+      </c>
+      <c r="E462" t="s">
+        <v>26</v>
+      </c>
+      <c r="F462" t="s">
+        <v>19</v>
+      </c>
+      <c r="G462" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>25</v>
+      </c>
+      <c r="B463">
         <f>(1/0.053177)*0.125938218719691</f>
         <v>2.3682836323916541</v>
       </c>
-      <c r="C462" t="s">
-        <v>165</v>
-      </c>
-      <c r="D462" t="s">
-        <v>4</v>
-      </c>
-      <c r="E462" t="s">
+      <c r="C463" t="s">
+        <v>165</v>
+      </c>
+      <c r="D463" t="s">
+        <v>4</v>
+      </c>
+      <c r="E463" t="s">
         <v>26</v>
       </c>
-      <c r="F462" t="s">
-        <v>19</v>
-      </c>
-      <c r="G462" t="s">
+      <c r="F463" t="s">
+        <v>19</v>
+      </c>
+      <c r="G463" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A464" s="1" t="s">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A465" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B464" s="1" t="s">
+      <c r="B465" s="1" t="s">
         <v>205</v>
-      </c>
-    </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A465" t="s">
-        <v>3</v>
-      </c>
-      <c r="B465" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B466" t="s">
-        <v>226</v>
+        <v>4</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B467" t="s">
-        <v>28</v>
+        <v>226</v>
       </c>
     </row>
     <row r="468" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B468" t="s">
-        <v>225</v>
+        <v>28</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B469" t="s">
-        <v>7</v>
+        <v>225</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
+        <v>6</v>
+      </c>
+      <c r="B470" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
         <v>216</v>
       </c>
-      <c r="B470" t="s">
+      <c r="B471" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A471" s="1" t="s">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A472" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B471" s="1"/>
-      <c r="C471" s="1"/>
-      <c r="D471" s="1"/>
-      <c r="E471" s="1"/>
-      <c r="F471" s="1"/>
-      <c r="G471" s="1"/>
-      <c r="H471" s="1"/>
-      <c r="I471" s="1"/>
-      <c r="J471" s="1"/>
-      <c r="K471" s="1"/>
-    </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A472" t="s">
-        <v>9</v>
-      </c>
-      <c r="B472" t="s">
-        <v>10</v>
-      </c>
-      <c r="C472" t="s">
-        <v>11</v>
-      </c>
-      <c r="D472" t="s">
-        <v>3</v>
-      </c>
-      <c r="E472" t="s">
-        <v>6</v>
-      </c>
-      <c r="F472" t="s">
-        <v>13</v>
-      </c>
-      <c r="G472" t="s">
-        <v>5</v>
-      </c>
-      <c r="H472" t="s">
-        <v>2</v>
-      </c>
+      <c r="B472" s="1"/>
+      <c r="C472" s="1"/>
+      <c r="D472" s="1"/>
+      <c r="E472" s="1"/>
+      <c r="F472" s="1"/>
+      <c r="G472" s="1"/>
+      <c r="H472" s="1"/>
+      <c r="I472" s="1"/>
+      <c r="J472" s="1"/>
+      <c r="K472" s="1"/>
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>205</v>
-      </c>
-      <c r="B473">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B473" t="s">
+        <v>10</v>
       </c>
       <c r="C473" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="D473" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E473" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F473" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G473" t="s">
-        <v>226</v>
+        <v>5</v>
+      </c>
+      <c r="H473" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
+        <v>205</v>
+      </c>
+      <c r="B474">
+        <v>1</v>
+      </c>
+      <c r="C474" t="s">
+        <v>164</v>
+      </c>
+      <c r="D474" t="s">
+        <v>4</v>
+      </c>
+      <c r="E474" t="s">
+        <v>7</v>
+      </c>
+      <c r="F474" t="s">
+        <v>18</v>
+      </c>
+      <c r="G474" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
         <v>169</v>
       </c>
-      <c r="B474">
+      <c r="B475">
         <f>(1/0.045)*0.0085612534146254</f>
         <v>0.19025007588056442</v>
       </c>
-      <c r="C474" t="s">
+      <c r="C475" t="s">
         <v>164</v>
       </c>
-      <c r="D474" t="s">
-        <v>4</v>
-      </c>
-      <c r="E474" t="s">
-        <v>7</v>
-      </c>
-      <c r="F474" t="s">
-        <v>19</v>
-      </c>
-      <c r="G474" t="s">
+      <c r="D475" t="s">
+        <v>4</v>
+      </c>
+      <c r="E475" t="s">
+        <v>7</v>
+      </c>
+      <c r="F475" t="s">
+        <v>19</v>
+      </c>
+      <c r="G475" t="s">
         <v>168</v>
       </c>
-      <c r="H474" t="s">
+      <c r="H475" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A475" t="s">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
         <v>192</v>
       </c>
-      <c r="B475">
+      <c r="B476">
         <f>(1/0.045)*0.0109585812086088</f>
         <v>0.24352402685797334</v>
       </c>
-      <c r="C475" t="s">
+      <c r="C476" t="s">
         <v>164</v>
       </c>
-      <c r="D475" t="s">
-        <v>4</v>
-      </c>
-      <c r="E475" t="s">
-        <v>7</v>
-      </c>
-      <c r="F475" t="s">
-        <v>19</v>
-      </c>
-      <c r="G475" t="s">
+      <c r="D476" t="s">
+        <v>4</v>
+      </c>
+      <c r="E476" t="s">
+        <v>7</v>
+      </c>
+      <c r="F476" t="s">
+        <v>19</v>
+      </c>
+      <c r="G476" t="s">
         <v>193</v>
       </c>
-      <c r="H475" t="s">
+      <c r="H476" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A476" t="s">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
         <v>195</v>
       </c>
-      <c r="B476">
+      <c r="B477">
         <f>(1/0.045)*0.0154881832669088</f>
         <v>0.34418185037575111</v>
       </c>
-      <c r="C476" t="s">
+      <c r="C477" t="s">
         <v>164</v>
       </c>
-      <c r="D476" t="s">
-        <v>4</v>
-      </c>
-      <c r="E476" t="s">
-        <v>7</v>
-      </c>
-      <c r="F476" t="s">
-        <v>19</v>
-      </c>
-      <c r="G476" t="s">
+      <c r="D477" t="s">
+        <v>4</v>
+      </c>
+      <c r="E477" t="s">
+        <v>7</v>
+      </c>
+      <c r="F477" t="s">
+        <v>19</v>
+      </c>
+      <c r="G477" t="s">
         <v>196</v>
       </c>
-      <c r="H476" t="s">
+      <c r="H477" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A477" t="s">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
         <v>201</v>
       </c>
-      <c r="B477">
+      <c r="B478">
         <f>(1/0.045)*0.00937223587605556</f>
         <v>0.20827190835679019</v>
       </c>
-      <c r="C477" t="s">
+      <c r="C478" t="s">
         <v>164</v>
       </c>
-      <c r="D477" t="s">
-        <v>4</v>
-      </c>
-      <c r="E477" t="s">
-        <v>7</v>
-      </c>
-      <c r="F477" t="s">
-        <v>19</v>
-      </c>
-      <c r="G477" t="s">
+      <c r="D478" t="s">
+        <v>4</v>
+      </c>
+      <c r="E478" t="s">
+        <v>7</v>
+      </c>
+      <c r="F478" t="s">
+        <v>19</v>
+      </c>
+      <c r="G478" t="s">
         <v>202</v>
       </c>
-      <c r="H477" t="s">
+      <c r="H478" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A478" t="s">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
         <v>86</v>
       </c>
-      <c r="B478">
+      <c r="B479">
         <f>(1/0.045)*0.000592324289244388</f>
         <v>1.3162761983208621E-2</v>
       </c>
-      <c r="C478" t="s">
-        <v>165</v>
-      </c>
-      <c r="D478" t="s">
+      <c r="C479" t="s">
+        <v>165</v>
+      </c>
+      <c r="D479" t="s">
         <v>21</v>
       </c>
-      <c r="E478" t="s">
-        <v>7</v>
-      </c>
-      <c r="F478" t="s">
-        <v>19</v>
-      </c>
-      <c r="G478" t="s">
+      <c r="E479" t="s">
+        <v>7</v>
+      </c>
+      <c r="F479" t="s">
+        <v>19</v>
+      </c>
+      <c r="G479" t="s">
         <v>163</v>
-      </c>
-      <c r="H478" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A479" t="s">
-        <v>25</v>
-      </c>
-      <c r="B479">
-        <f>(1/0.045)*0.105117512875205</f>
-        <v>2.3359447305601111</v>
-      </c>
-      <c r="C479" t="s">
-        <v>165</v>
-      </c>
-      <c r="D479" t="s">
-        <v>4</v>
-      </c>
-      <c r="E479" t="s">
-        <v>26</v>
-      </c>
-      <c r="F479" t="s">
-        <v>19</v>
-      </c>
-      <c r="G479" t="s">
-        <v>62</v>
       </c>
       <c r="H479" t="s">
         <v>217</v>
@@ -8906,428 +8926,433 @@
         <v>25</v>
       </c>
       <c r="B480">
+        <f>(1/0.045)*0.105117512875205</f>
+        <v>2.3359447305601111</v>
+      </c>
+      <c r="C480" t="s">
+        <v>165</v>
+      </c>
+      <c r="D480" t="s">
+        <v>4</v>
+      </c>
+      <c r="E480" t="s">
+        <v>26</v>
+      </c>
+      <c r="F480" t="s">
+        <v>19</v>
+      </c>
+      <c r="G480" t="s">
+        <v>62</v>
+      </c>
+      <c r="H480" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>25</v>
+      </c>
+      <c r="B481">
         <f>(1/0.045)*0.0936148404555879</f>
         <v>2.0803297879019533</v>
       </c>
-      <c r="C480" t="s">
-        <v>165</v>
-      </c>
-      <c r="D480" t="s">
-        <v>4</v>
-      </c>
-      <c r="E480" t="s">
+      <c r="C481" t="s">
+        <v>165</v>
+      </c>
+      <c r="D481" t="s">
+        <v>4</v>
+      </c>
+      <c r="E481" t="s">
         <v>26</v>
       </c>
-      <c r="F480" t="s">
-        <v>19</v>
-      </c>
-      <c r="G480" t="s">
+      <c r="F481" t="s">
+        <v>19</v>
+      </c>
+      <c r="G481" t="s">
         <v>62</v>
       </c>
-      <c r="H480" t="s">
+      <c r="H481" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="482" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="2" t="s">
+    <row r="483" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A483" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B482" s="2" t="s">
+      <c r="B483" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="483" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="3" t="s">
+    <row r="484" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A484" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B483" s="3" t="s">
+      <c r="B484" s="3" t="s">
         <v>253</v>
-      </c>
-    </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A484" t="s">
-        <v>3</v>
-      </c>
-      <c r="B484" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>230</v>
-      </c>
-      <c r="B485">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B485" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="486" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>5</v>
-      </c>
-      <c r="B486" t="s">
-        <v>254</v>
+        <v>230</v>
+      </c>
+      <c r="B486">
+        <v>1</v>
       </c>
     </row>
     <row r="487" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B487" t="s">
-        <v>7</v>
+        <v>254</v>
       </c>
     </row>
     <row r="488" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
+        <v>6</v>
+      </c>
+      <c r="B488" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
         <v>216</v>
       </c>
-      <c r="B488" t="s">
+      <c r="B489" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A489" s="1" t="s">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A490" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
-        <v>9</v>
-      </c>
-      <c r="B490" t="s">
-        <v>10</v>
-      </c>
-      <c r="C490" t="s">
-        <v>6</v>
-      </c>
-      <c r="D490" t="s">
-        <v>12</v>
-      </c>
-      <c r="E490" t="s">
-        <v>3</v>
-      </c>
-      <c r="F490" t="s">
-        <v>13</v>
-      </c>
-      <c r="G490" t="s">
-        <v>5</v>
-      </c>
-      <c r="H490" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>238</v>
-      </c>
-      <c r="B491">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B491" t="s">
+        <v>10</v>
       </c>
       <c r="C491" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D491" t="s">
+        <v>12</v>
       </c>
       <c r="E491" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F491" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G491" t="s">
-        <v>254</v>
+        <v>5</v>
+      </c>
+      <c r="H491" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
+        <v>238</v>
+      </c>
+      <c r="B492">
+        <v>1</v>
+      </c>
+      <c r="C492" t="s">
+        <v>7</v>
+      </c>
+      <c r="E492" t="s">
+        <v>21</v>
+      </c>
+      <c r="F492" t="s">
+        <v>18</v>
+      </c>
+      <c r="G492" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
         <v>203</v>
       </c>
-      <c r="B492" s="4">
+      <c r="B493" s="4">
         <f>408*0.046/24.971</f>
         <v>0.75159184654198874</v>
       </c>
-      <c r="C492" t="s">
-        <v>7</v>
-      </c>
-      <c r="E492" t="s">
-        <v>4</v>
-      </c>
-      <c r="F492" t="s">
-        <v>19</v>
-      </c>
-      <c r="G492" t="s">
+      <c r="C493" t="s">
+        <v>7</v>
+      </c>
+      <c r="E493" t="s">
+        <v>4</v>
+      </c>
+      <c r="F493" t="s">
+        <v>19</v>
+      </c>
+      <c r="G493" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A493" t="s">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
         <v>239</v>
       </c>
-      <c r="B493" s="4">
+      <c r="B494" s="4">
         <f>0.275/24.971</f>
         <v>1.1012774818789798E-2</v>
       </c>
-      <c r="C493" t="s">
-        <v>7</v>
-      </c>
-      <c r="E493" t="s">
+      <c r="C494" t="s">
+        <v>7</v>
+      </c>
+      <c r="E494" t="s">
         <v>21</v>
       </c>
-      <c r="F493" t="s">
-        <v>19</v>
-      </c>
-      <c r="G493" t="s">
+      <c r="F494" t="s">
+        <v>19</v>
+      </c>
+      <c r="G494" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
         <v>241</v>
       </c>
-      <c r="B494" s="4">
+      <c r="B495" s="4">
         <f>0.593/24.971</f>
         <v>2.3747547154699448E-2</v>
       </c>
-      <c r="C494" t="s">
-        <v>7</v>
-      </c>
-      <c r="E494" t="s">
+      <c r="C495" t="s">
+        <v>7</v>
+      </c>
+      <c r="E495" t="s">
         <v>21</v>
       </c>
-      <c r="F494" t="s">
-        <v>19</v>
-      </c>
-      <c r="G494" t="s">
+      <c r="F495" t="s">
+        <v>19</v>
+      </c>
+      <c r="G495" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="495" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A495" s="3" t="s">
+    <row r="496" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A496" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B495" s="5">
+      <c r="B496" s="5">
         <f>0.085/24.971</f>
         <v>3.4039485803532099E-3</v>
       </c>
-      <c r="C495" t="s">
-        <v>7</v>
-      </c>
-      <c r="E495" t="s">
+      <c r="C496" t="s">
+        <v>7</v>
+      </c>
+      <c r="E496" t="s">
         <v>21</v>
       </c>
-      <c r="F495" t="s">
-        <v>19</v>
-      </c>
-      <c r="G495" t="s">
+      <c r="F496" t="s">
+        <v>19</v>
+      </c>
+      <c r="G496" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
         <v>245</v>
       </c>
-      <c r="B496" s="6">
+      <c r="B497" s="6">
         <f>2.75/24.971</f>
         <v>0.11012774818789796</v>
       </c>
-      <c r="C496" t="s">
-        <v>7</v>
-      </c>
-      <c r="E496" t="s">
+      <c r="C497" t="s">
+        <v>7</v>
+      </c>
+      <c r="E497" t="s">
         <v>21</v>
       </c>
-      <c r="F496" t="s">
-        <v>19</v>
-      </c>
-      <c r="G496" t="s">
+      <c r="F497" t="s">
+        <v>19</v>
+      </c>
+      <c r="G497" t="s">
         <v>246</v>
       </c>
-      <c r="I496" s="7"/>
-      <c r="J496" s="8"/>
-      <c r="K496" s="8"/>
-    </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
+      <c r="I497" s="7"/>
+      <c r="J497" s="8"/>
+      <c r="K497" s="8"/>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
         <v>247</v>
       </c>
-      <c r="B497" s="6">
+      <c r="B498" s="6">
         <f>2.5/24.971</f>
         <v>0.10011613471627087</v>
       </c>
-      <c r="C497" t="s">
-        <v>7</v>
-      </c>
-      <c r="E497" t="s">
+      <c r="C498" t="s">
+        <v>7</v>
+      </c>
+      <c r="E498" t="s">
         <v>21</v>
       </c>
-      <c r="F497" t="s">
-        <v>19</v>
-      </c>
-      <c r="G497" t="s">
+      <c r="F498" t="s">
+        <v>19</v>
+      </c>
+      <c r="G498" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
         <v>248</v>
       </c>
-      <c r="B498" s="6">
+      <c r="B499" s="6">
         <f>2.75/24.971</f>
         <v>0.11012774818789796</v>
       </c>
-      <c r="C498" t="s">
-        <v>7</v>
-      </c>
-      <c r="E498" t="s">
+      <c r="C499" t="s">
+        <v>7</v>
+      </c>
+      <c r="E499" t="s">
         <v>21</v>
       </c>
-      <c r="F498" t="s">
-        <v>19</v>
-      </c>
-      <c r="G498" t="s">
+      <c r="F499" t="s">
+        <v>19</v>
+      </c>
+      <c r="G499" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
         <v>250</v>
       </c>
-      <c r="B499" s="9">
+      <c r="B500" s="9">
         <f>2.5/24.971</f>
         <v>0.10011613471627087</v>
       </c>
-      <c r="C499" t="s">
-        <v>7</v>
-      </c>
-      <c r="E499" t="s">
+      <c r="C500" t="s">
+        <v>7</v>
+      </c>
+      <c r="E500" t="s">
         <v>21</v>
       </c>
-      <c r="F499" t="s">
-        <v>19</v>
-      </c>
-      <c r="G499" t="s">
+      <c r="F500" t="s">
+        <v>19</v>
+      </c>
+      <c r="G500" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B500" s="10"/>
-    </row>
-    <row r="501" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A501" s="2" t="s">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B501" s="10"/>
+    </row>
+    <row r="502" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A502" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B501" s="2" t="s">
+      <c r="B502" s="2" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>2</v>
-      </c>
-      <c r="B502" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B503" t="s">
-        <v>21</v>
+        <v>256</v>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>230</v>
-      </c>
-      <c r="B504">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B504" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>5</v>
-      </c>
-      <c r="B505" t="s">
-        <v>237</v>
+        <v>230</v>
+      </c>
+      <c r="B505">
+        <v>1</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B506" t="s">
-        <v>7</v>
+        <v>237</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
+        <v>6</v>
+      </c>
+      <c r="B507" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
         <v>216</v>
       </c>
-      <c r="B507" t="s">
+      <c r="B508" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A508" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B508" s="1"/>
-      <c r="C508" s="1"/>
-      <c r="D508" s="1"/>
-      <c r="E508" s="1"/>
-      <c r="F508" s="1"/>
-      <c r="G508" s="1"/>
     </row>
     <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B509" s="1"/>
+      <c r="C509" s="1"/>
+      <c r="D509" s="1"/>
+      <c r="E509" s="1"/>
+      <c r="F509" s="1"/>
+      <c r="G509" s="1"/>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A510" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B509" s="1" t="s">
+      <c r="B510" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C509" s="1" t="s">
+      <c r="C510" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D509" s="1" t="s">
+      <c r="D510" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E509" s="1" t="s">
+      <c r="E510" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F509" s="1" t="s">
+      <c r="F510" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G509" s="1" t="s">
+      <c r="G510" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H509" s="1" t="s">
+      <c r="H510" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="510" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A510" s="3" t="str">
-        <f>B501</f>
+    <row r="511" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A511" s="3" t="str">
+        <f>B502</f>
         <v>market for battery, Sodium-ion, SiB</v>
-      </c>
-      <c r="B510">
-        <v>1</v>
-      </c>
-      <c r="C510" t="s">
-        <v>7</v>
-      </c>
-      <c r="E510" t="str">
-        <f>B503</f>
-        <v>GLO</v>
-      </c>
-      <c r="F510" t="s">
-        <v>18</v>
-      </c>
-      <c r="G510" t="str">
-        <f>B505</f>
-        <v>battery, SiB</v>
-      </c>
-    </row>
-    <row r="511" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A511" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="B511">
         <v>1</v>
@@ -9335,25 +9360,27 @@
       <c r="C511" t="s">
         <v>7</v>
       </c>
-      <c r="E511" t="s">
-        <v>21</v>
+      <c r="E511" t="str">
+        <f>B504</f>
+        <v>GLO</v>
       </c>
       <c r="F511" t="s">
-        <v>19</v>
-      </c>
-      <c r="G511" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A512" t="s">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="G511" t="str">
+        <f>B506</f>
+        <v>battery, SiB</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A512" s="3" t="s">
+        <v>252</v>
       </c>
       <c r="B512">
-        <v>0.30910727700000001</v>
+        <v>1</v>
       </c>
       <c r="C512" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E512" t="s">
         <v>21</v>
@@ -9362,15 +9389,15 @@
         <v>19</v>
       </c>
       <c r="G512" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>231</v>
+        <v>27</v>
       </c>
       <c r="B513">
-        <v>2.4627409999999999E-2</v>
+        <v>0.30910727700000001</v>
       </c>
       <c r="C513" t="s">
         <v>24</v>
@@ -9382,15 +9409,15 @@
         <v>19</v>
       </c>
       <c r="G513" t="s">
-        <v>232</v>
+        <v>34</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B514">
-        <v>0.20877976500000001</v>
+        <v>2.4627409999999999E-2</v>
       </c>
       <c r="C514" t="s">
         <v>24</v>
@@ -9402,15 +9429,15 @@
         <v>19</v>
       </c>
       <c r="G514" t="s">
-        <v>33</v>
+        <v>232</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B515">
-        <v>0.59901584900000004</v>
+        <v>0.20877976500000001</v>
       </c>
       <c r="C515" t="s">
         <v>24</v>
@@ -9422,14 +9449,34 @@
         <v>19</v>
       </c>
       <c r="G515" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>234</v>
+      </c>
+      <c r="B516">
+        <v>0.59901584900000004</v>
+      </c>
+      <c r="C516" t="s">
+        <v>24</v>
+      </c>
+      <c r="E516" t="s">
+        <v>21</v>
+      </c>
+      <c r="F516" t="s">
+        <v>19</v>
+      </c>
+      <c r="G516" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A516" s="3"/>
+    <row r="517" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A517" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K480" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K481" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/premise/data/additional_inventories/lci-batteries-SIB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-SIB.xlsx
@@ -8987,8 +8987,12 @@
       <c r="A484" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B484" s="3" t="s">
-        <v>253</v>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>APPROVED SODIUM-ION PRODUCTION-EXCHANGE IDENTITY, 2026-10-18. The parent activity is battery module production, for SiB battery, with output battery, SiB module. Correct only the copied LiS production-exchange name to match the SIB parent. Product, reference amount, cell fraction, all recipe coefficients and existing capacity normalization remain unchanged. This is an identity correction; no numerical system-metal effect or complete equipment coverage is established.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Taken from Wickerts et al. (2023). Prospective Life Cycle Assessment of Lithium-Sulfur Batteries for Stationary Energy Storage. ACS Sustainable Chemistry &amp; Engineering. Based on Ainsworth (2016), Peters and Weil (2017), Ellingsen et al. (2014) and adapted to SiB battery cells.</t>
+        </is>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.25">
@@ -9063,8 +9067,10 @@
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A492" t="s">
-        <v>238</v>
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>battery module production, for SiB battery</t>
+        </is>
       </c>
       <c r="B492">
         <v>1</v>

--- a/premise/data/additional_inventories/lci-batteries-SIB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-SIB.xlsx
@@ -1264,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K517"/>
+  <dimension ref="A1:K559"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" customWidth="1"/>
@@ -9481,6 +9481,978 @@
     <row r="517" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" s="3"/>
     </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B529">
+        <v>1</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>battery cell production, SIB, with NMMT cathode and fossil-HC anode</t>
+        </is>
+      </c>
+      <c r="B530">
+        <v>1</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>battery cell</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>battery cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>market group for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B531">
+        <v>0.309107277</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="B532">
+        <v>0.02462741</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B533">
+        <v>0.208779765</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B534">
+        <v>0.599015849</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B535">
+        <v>-1</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B540">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B547">
+        <v>1</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>aluminium busbar production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B548">
+        <v>0.09332866350638845</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>aluminium busbar</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>aluminium busbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>bimetallic busbar production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B549">
+        <v>0.20125053621559394</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>bimetallic busbar</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>bimetallic busbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>copper busbar production, for LiS battery</t>
+        </is>
+      </c>
+      <c r="B550">
+        <v>0.028847041447429153</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>copper busbar</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>copper busbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B551">
+        <v>0.9332866350638843</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B552">
+        <v>0.8484423955126221</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>market for injection moulding</t>
+        </is>
+      </c>
+      <c r="B553">
+        <v>0.9332866350638843</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>market for metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B554">
+        <v>0.8484423955126221</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>market group for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B555">
+        <v>0.6507188137115758</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="B556">
+        <v>0.051844521990948134</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B557">
+        <v>0.4395138229236239</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B558">
+        <v>1.2610213723817068</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B559">
+        <v>-2.1051552717459177</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K481" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-SIB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-SIB.xlsx
@@ -1595,8 +1595,12 @@
       <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B24" t="s">
-        <v>221</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>APPROVED REFINED-NICKEL SUPPLY BOUNDARY, issue84, 2026-10-18. Zhang et al.2024 DOI10.1016/j.resconrec.2023.107362, inherited nickel-plating inventory; original9.37g Ni/m2 retained as gross nickel supply reference, not newly measured coating mass. The finishing process formerly extracted0.00937kg Nickel directly from ground, bypassing mining/refining supply and refined-metal exchange indicators. Replace that one resource exchange with0.00937kg existing market for nickel,class1,GLO. Remove the direct resource extraction at the coating operation to avoid charging both local extraction and supplier extraction. Preserve existing electricity0.0427kWh/m2,8kgwater,wastewater,0.000472kg residue and Ni emissions0.000000374kgair+0.000016kgwater. Gross Ni dose is not a measured retained-film mass: after those two explicit emissions,at most0.009353626kg/m2 remains before unknown residue Ni. No assumed thickness,100%deposition,closed-loop bath,hydrometallurgy reagent reconstruction or recycling credit. Salt speciation,bathmakeup,anode/cathodeefficiency,dragout and residuecomposition remain gaps;class1Ni is a feed boundary reference,not proof of industrial bath design. Preserve casing area,cell chemistry/energy density and all perMJ vehicle coefficients. Existing native Nickel supply and primary-secondaryshares untouched; only this workbook plating input is changed.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Zhang, S., Steubing, B., Potter, H. K., Hansson, P. A., &amp; Nordberg, Å. (2024). Future climate impacts of sodium-ion batteries. Resources, Conservation and Recycling, 202, 107362. https://doi.org/10.1016/j.resconrec.2023.107362</t>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1693,23 +1697,39 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>210</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
       </c>
       <c r="B32">
-        <v>9.3699999999999999E-3</v>
-      </c>
-      <c r="C32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>155</v>
-      </c>
-      <c r="G32" t="s">
-        <v>17</v>
+        <v>0.00937</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ei_3.9.1_cutoff</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F32"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">

--- a/premise/data/additional_inventories/lci-batteries-SIB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-SIB.xlsx
@@ -1264,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K559"/>
+  <dimension ref="A1:K611"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" customWidth="1"/>
@@ -3300,8 +3300,12 @@
       <c r="A136" t="s">
         <v>2</v>
       </c>
-      <c r="B136" t="s">
-        <v>221</v>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Zhang, S., Steubing, B., Potter, H. K., Hansson, P. A., &amp; Nordberg, Å. (2024). Future climate impacts of sodium-ion batteries. Resources, Conservation and Recycling, 202, 107362. https://doi.org/10.1016/j.resconrec.2023.107362</t>
+        </is>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -3439,8 +3443,10 @@
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>181</v>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+        </is>
       </c>
       <c r="B147">
         <v>2.75E-2</v>
@@ -3448,8 +3454,10 @@
       <c r="C147" t="s">
         <v>164</v>
       </c>
-      <c r="D147" t="s">
-        <v>4</v>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E147" t="s">
         <v>7</v>
@@ -3457,8 +3465,10 @@
       <c r="G147" t="s">
         <v>19</v>
       </c>
-      <c r="H147" t="s">
-        <v>182</v>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+        </is>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -5470,8 +5480,12 @@
       <c r="A267" t="s">
         <v>2</v>
       </c>
-      <c r="B267" t="s">
-        <v>221</v>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Zhang, S., Steubing, B., Potter, H. K., Hansson, P. A., &amp; Nordberg, Å. (2024). Future climate impacts of sodium-ion batteries. Resources, Conservation and Recycling, 202, 107362. https://doi.org/10.1016/j.resconrec.2023.107362</t>
+        </is>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
@@ -10473,6 +10487,1064 @@
         </is>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B564">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+        </is>
+      </c>
+      <c r="B571">
+        <v>1</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>market for magnesium oxide</t>
+        </is>
+      </c>
+      <c r="B572">
+        <v>0.4233391103408434</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>magnesium oxide</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>magnesium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>market for hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="B573">
+        <v>0.7658841447402973</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B574">
+        <v>2</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B575">
+        <v>0.5</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B576">
+        <v>0.00018922325508114067</v>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B581">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+        </is>
+      </c>
+      <c r="B588">
+        <v>1</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+        </is>
+      </c>
+      <c r="B589">
+        <v>0.0162435693317292</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="B590">
+        <v>0.9837564306682708</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B595">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+        </is>
+      </c>
+      <c r="B602">
+        <v>1</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>market for lime, hydrated, loose weight</t>
+        </is>
+      </c>
+      <c r="B603">
+        <v>1.3373270966129123</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>lime, hydrated, loose weight</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>lime, hydrated, loose weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+        </is>
+      </c>
+      <c r="B604">
+        <v>105.79</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B605">
+        <v>0.12</v>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B606">
+        <v>1.78</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>market group for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B607">
+        <v>0.717</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B608">
+        <v>-0.10607469551766555</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B609">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Heat, waste</t>
+        </is>
+      </c>
+      <c r="B610">
+        <v>6.42</v>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Occupation, mineral extraction site</t>
+        </is>
+      </c>
+      <c r="B611">
+        <v>1.63</v>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>square meter-year</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>natural resource::land</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K481" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-SIB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-SIB.xlsx
@@ -3445,7 +3445,7 @@
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="inlineStr">
         <is>
-          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+          <t xml:space="preserve">magnesium hydroxide production, precipitation</t>
         </is>
       </c>
       <c r="B147">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,8 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Sodium-ion, SiB, density-scaled reference. Former reference product: market for battery cells, Sodium-ion, SiB, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9655,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B529">
@@ -9677,12 +9678,12 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>market for battery cells, Sodium-ion, SiB, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -9904,7 +9905,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9939,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9975,9 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10038,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
       <c r="B547">
@@ -10058,12 +10061,12 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10498,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10532,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10568,8 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: magnesium chloride, primary synthetic brine-equivalent engineering reference. Former reference product: magnesium chloride, primary synthetic brine-equivalent engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10630,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
         </is>
       </c>
       <c r="B571">
@@ -10649,12 +10653,12 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10840,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10874,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10910,8 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: magnesium-bearing brine, explicit MgCl2 engineering reference. Former reference product: magnesium-bearing brine, explicit MgCl2 engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -10967,7 +10972,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
         </is>
       </c>
       <c r="B588">
@@ -10990,19 +10995,19 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
         </is>
       </c>
       <c r="B589">
@@ -11025,12 +11030,12 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>magnesium chloride, primary synthetic brine-equivalent engineering reference</t>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11082,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+          <t xml:space="preserve">magnesium hydroxide production, precipitation</t>
         </is>
       </c>
     </row>
@@ -11111,7 +11116,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11152,8 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: magnesium hydroxide, balanced precipitation engineering reference. Former reference product: magnesium hydroxide, balanced precipitation engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11214,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+          <t xml:space="preserve">magnesium hydroxide production, precipitation</t>
         </is>
       </c>
       <c r="B602">
@@ -11231,12 +11237,12 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>magnesium hydroxide, balanced precipitation engineering reference</t>
+          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11284,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
         </is>
       </c>
       <c r="B604">
@@ -11301,12 +11307,12 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>magnesium-bearing brine, explicit MgCl2 engineering reference</t>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-SIB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-SIB.xlsx
@@ -9939,7 +9939,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Sodium-ion, SiB, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -9975,7 +9975,8 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -10051,7 +10052,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -10061,12 +10062,12 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Sodium-ion, SiB, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Sodium-ion, SiB, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-SIB.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-SIB.xlsx
@@ -1264,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K611"/>
+  <dimension ref="A1:K616"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.28515625" customWidth="1"/>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
+          <t xml:space="preserve">market for battery cell, sodium-ion, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9581,9 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+          <t xml:space="preserve">Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.
+Explicit reference links (source or inherited supplier evidence; the engineering adaptation is documented in the activity comment): https://doi.org/10.1016/j.resconrec.2023.107362
+Supplier lineage: battery cell production, SIB, with NMMT cathode and fossil-HC anode.</t>
         </is>
       </c>
     </row>
@@ -9601,96 +9603,73 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E528" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F528" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I528" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
-        </is>
-      </c>
-      <c r="B529">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>production</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>battery cell production, SIB, with NMMT cathode and fossil-HC anode</t>
+          <t xml:space="preserve">market for battery cell, sodium-ion, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B530">
@@ -9698,7 +9677,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -9708,37 +9687,37 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>battery cell</t>
+          <t xml:space="preserve">battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>battery cell</t>
+          <t xml:space="preserve">battery cell, Sodium-ion, SiB, including end-of-life treatment</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>market group for transport, freight train</t>
+          <t>battery cell production, SIB, with NMMT cathode and fossil-HC anode</t>
         </is>
       </c>
       <c r="B531">
-        <v>0.309107277</v>
+        <v>1</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>ton kilometer</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -9748,23 +9727,23 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t>battery cell</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t>battery cell</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>market group for transport, freight, inland waterways, barge</t>
+          <t>market group for transport, freight train</t>
         </is>
       </c>
       <c r="B532">
-        <v>0.02462741</v>
+        <v>0.309107277</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
@@ -9783,23 +9762,23 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>transport, freight, inland waterways, barge</t>
+          <t>transport, freight train</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>transport, freight, inland waterways, barge</t>
+          <t>transport, freight train</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>market group for transport, freight, lorry, unspecified</t>
+          <t>market group for transport, freight, inland waterways, barge</t>
         </is>
       </c>
       <c r="B533">
-        <v>0.208779765</v>
+        <v>0.02462741</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
@@ -9818,23 +9797,23 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>transport, freight, lorry, unspecified</t>
+          <t>transport, freight, inland waterways, barge</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>transport, freight, lorry, unspecified</t>
+          <t>transport, freight, inland waterways, barge</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>market for transport, freight, sea, container ship</t>
+          <t>market group for transport, freight, lorry, unspecified</t>
         </is>
       </c>
       <c r="B534">
-        <v>0.599015849</v>
+        <v>0.208779765</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
@@ -9853,127 +9832,164 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>transport, freight, sea, container ship</t>
+          <t>transport, freight, lorry, unspecified</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>transport, freight, sea, container ship</t>
+          <t>transport, freight, lorry, unspecified</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B535">
+        <v>0.599015849</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
           <t>market for used Li-ion battery</t>
         </is>
       </c>
-      <c r="B535">
+      <c r="B536">
         <v>-1</v>
       </c>
-      <c r="C535" t="inlineStr">
+      <c r="C536" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr">
+      <c r="D536" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F535" t="inlineStr">
+      <c r="F536" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G535" t="inlineStr">
+      <c r="G536" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>
       </c>
-      <c r="I535" t="inlineStr">
+      <c r="I536" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, sodium-ion, without cells and controls</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B540">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B541">
+        <v>1</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t xml:space="preserve">kilowatt hour</t>
+          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.
+Explicit reference links (source or inherited supplier evidence; the engineering adaptation is documented in the activity comment): https://doi.org/10.1021/acssuschemeng.3c00141
+Supplier lineage: aluminium busbar production, for LiS battery ; bimetallic busbar production, for LiS battery ; copper busbar production, for LiS battery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B545" t="inlineStr">
         <is>
           <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
 Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Sodium-ion, SiB, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
@@ -9982,138 +9998,80 @@
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E546" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G546" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H546" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I546" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack component production and end-of-life treatment, Sodium-ion, SiB, without cells and controls</t>
-        </is>
-      </c>
-      <c r="B547">
-        <v>1</v>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F547" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
-        </is>
-      </c>
-      <c r="I547" t="inlineStr">
-        <is>
-          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>aluminium busbar production, for LiS battery</t>
-        </is>
-      </c>
-      <c r="B548">
-        <v>0.09332866350638845</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>aluminium busbar</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>aluminium busbar</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>bimetallic busbar production, for LiS battery</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, sodium-ion, without cells and controls</t>
         </is>
       </c>
       <c r="B549">
-        <v>0.20125053621559394</v>
+        <v>1</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -10122,33 +10080,33 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>bimetallic busbar</t>
+          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>bimetallic busbar</t>
+          <t xml:space="preserve">battery pack component provision, Sodium-ion, SiB, without cells and controls</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>copper busbar production, for LiS battery</t>
+          <t>aluminium busbar production, for LiS battery</t>
         </is>
       </c>
       <c r="B550">
-        <v>0.028847041447429153</v>
+        <v>0.09332866350638845</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -10167,23 +10125,23 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>copper busbar</t>
+          <t>aluminium busbar</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>copper busbar</t>
+          <t>aluminium busbar</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>market for polypropylene, granulate</t>
+          <t>bimetallic busbar production, for LiS battery</t>
         </is>
       </c>
       <c r="B551">
-        <v>0.9332866350638843</v>
+        <v>0.20125053621559394</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -10202,23 +10160,23 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>polypropylene, granulate</t>
+          <t>bimetallic busbar</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>polypropylene, granulate</t>
+          <t>bimetallic busbar</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>market for steel, low-alloyed</t>
+          <t>copper busbar production, for LiS battery</t>
         </is>
       </c>
       <c r="B552">
-        <v>0.8484423955126221</v>
+        <v>0.028847041447429153</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
@@ -10237,19 +10195,19 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>copper busbar</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>steel, low-alloyed</t>
+          <t>copper busbar</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>market for injection moulding</t>
+          <t>market for polypropylene, granulate</t>
         </is>
       </c>
       <c r="B553">
@@ -10272,19 +10230,19 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>injection moulding</t>
+          <t>polypropylene, granulate</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
         <is>
-          <t>injection moulding</t>
+          <t>polypropylene, granulate</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>market for metal working, average for steel product manufacturing</t>
+          <t>market for steel, low-alloyed</t>
         </is>
       </c>
       <c r="B554">
@@ -10307,23 +10265,23 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>metal working, average for steel product manufacturing</t>
+          <t>steel, low-alloyed</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>market group for transport, freight train</t>
+          <t>market for injection moulding</t>
         </is>
       </c>
       <c r="B555">
-        <v>0.6507188137115758</v>
+        <v>0.9332866350638843</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -10332,7 +10290,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>ton kilometer</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
@@ -10342,23 +10300,23 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t>injection moulding</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t>injection moulding</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>market group for transport, freight, inland waterways, barge</t>
+          <t>market for metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="B556">
-        <v>0.051844521990948134</v>
+        <v>0.8484423955126221</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -10367,7 +10325,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>ton kilometer</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
@@ -10377,23 +10335,23 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>transport, freight, inland waterways, barge</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>transport, freight, inland waterways, barge</t>
+          <t>metal working, average for steel product manufacturing</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>market group for transport, freight, lorry, unspecified</t>
+          <t>market group for transport, freight train</t>
         </is>
       </c>
       <c r="B557">
-        <v>0.4395138229236239</v>
+        <v>0.6507188137115758</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -10412,23 +10370,23 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>transport, freight, lorry, unspecified</t>
+          <t>transport, freight train</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>transport, freight, lorry, unspecified</t>
+          <t>transport, freight train</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>market for transport, freight, sea, container ship</t>
+          <t>market group for transport, freight, inland waterways, barge</t>
         </is>
       </c>
       <c r="B558">
-        <v>1.2610213723817068</v>
+        <v>0.051844521990948134</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
@@ -10447,335 +10405,312 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>transport, freight, sea, container ship</t>
+          <t>transport, freight, inland waterways, barge</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>transport, freight, sea, container ship</t>
+          <t>transport, freight, inland waterways, barge</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
+          <t>market group for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B559">
+        <v>0.4395138229236239</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B560">
+        <v>1.2610213723817068</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
           <t>market for used Li-ion battery</t>
         </is>
       </c>
-      <c r="B559">
+      <c r="B561">
         <v>-2.1051552717459177</v>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C561" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr">
+      <c r="D561" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F559" t="inlineStr">
+      <c r="F561" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G559" t="inlineStr">
+      <c r="G561" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>
       </c>
-      <c r="I559" t="inlineStr">
+      <c r="I561" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B564">
-        <v>1</v>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
+        </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B566">
+        <v>1</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B568" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: magnesium chloride, primary synthetic brine-equivalent engineering reference. Former reference product: magnesium chloride, primary synthetic brine-equivalent engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F570" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G570" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H570" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I570" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
-        </is>
-      </c>
-      <c r="B571">
-        <v>1</v>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F571" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G571" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
-        </is>
-      </c>
-      <c r="I571" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>market for magnesium oxide</t>
-        </is>
-      </c>
-      <c r="B572">
-        <v>0.4233391103408434</v>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F572" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G572" t="inlineStr">
-        <is>
-          <t>magnesium oxide</t>
-        </is>
-      </c>
-      <c r="I572" t="inlineStr">
-        <is>
-          <t>magnesium oxide</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>market for hydrochloric acid, without water, in 30% solution state</t>
-        </is>
-      </c>
-      <c r="B573">
-        <v>0.7658841447402973</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>hydrochloric acid, without water, in 30% solution state</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>hydrochloric acid, without water, in 30% solution state</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
         </is>
       </c>
       <c r="B574">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for magnesium oxide</t>
         </is>
       </c>
       <c r="B575">
-        <v>0.5</v>
+        <v>0.4233391103408434</v>
       </c>
       <c r="C575" t="inlineStr">
         <is>
@@ -10784,7 +10719,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -10794,642 +10729,596 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>magnesium oxide</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>magnesium oxide</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>market for hydrochloric acid, without water, in 30% solution state</t>
         </is>
       </c>
       <c r="B576">
-        <v>0.00018922325508114067</v>
+        <v>0.7658841447402973</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>cubic meter</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>air::non-urban air or from high stacks</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>biosphere</t>
-        </is>
-      </c>
-      <c r="H576" t="inlineStr">
-        <is>
-          <t/>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>hydrochloric acid, without water, in 30% solution state</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B577">
+        <v>2</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B578">
+        <v>0.5</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B579" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
-        </is>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B580" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B581">
-        <v>1</v>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B579">
+        <v>0.00018922325508114067</v>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
+          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B584" t="inlineStr">
-        <is>
-          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B584">
+        <v>1</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B585" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: magnesium-bearing brine, explicit MgCl2 engineering reference. Former reference product: magnesium-bearing brine, explicit MgCl2 engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B587" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E587" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F587" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G587" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H587" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I587" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
-        </is>
-      </c>
-      <c r="B588">
-        <v>1</v>
-      </c>
-      <c r="C588" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F588" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G588" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
-        </is>
-      </c>
-      <c r="I588" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
-        </is>
-      </c>
-    </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
-        </is>
-      </c>
-      <c r="B589">
-        <v>0.0162435693317292</v>
-      </c>
-      <c r="C589" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F589" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
-        </is>
-      </c>
-      <c r="I589" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>market for tap water</t>
-        </is>
-      </c>
-      <c r="B590">
-        <v>0.9837564306682708</v>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D590" t="inlineStr">
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
+        </is>
+      </c>
+      <c r="B592">
+        <v>1</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F590" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G590" t="inlineStr">
-        <is>
-          <t>tap water</t>
-        </is>
-      </c>
-      <c r="I590" t="inlineStr">
-        <is>
-          <t>tap water</t>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B593" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium hydroxide production, precipitation</t>
+          <t xml:space="preserve">magnesium chloride production, from synthetic brine</t>
+        </is>
+      </c>
+      <c r="B593">
+        <v>0.0162435693317292</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magnesium chloride, from synthetic brine</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B594" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B595">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="B594">
+        <v>0.9837564306682708</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>tap water</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">magnesium hydroxide production, precipitation</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B599" t="inlineStr">
+      <c r="B603" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: magnesium hydroxide, balanced precipitation engineering reference. Former reference product: magnesium hydroxide, balanced precipitation engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED Mg-BEARING FEED AND PRECIPITATION REFERENCE, issue86, 2026-10-18. Peters et al.2016 DOI10.1039/C6EE00640J SI TableS11 and Zhang2024 DOI10.1016/j.resconrec.2023.107362:105.79kg NaCl-brine proxy,1.2kg hydratedlime and1.78kWh perkgMgOH2. https://www.rsc.org/suppdata/c6/ee/c6ee00640j/c6ee00640j1.pdf . These source proxies are NOT a chemical assay or measured yield. OriginalNaCl-brine contains no specifiedMg;1.2kgCaOH2 is below stoichiometric1.27045kg/kgpureMgOH2. Introduce a separately named balanced engineering recipe rather than pretend the original brine composition was measured. ReactionMgCl2+CaOH2-&gt;MgOH2+CaCl2. Assume95% recovery of precipitated product (90-100%sensitivity),100%MgCl2 precipitation then5%solidhandlingreject. GrossMgCl2=1.718407199603632kg andCaOH2=1.3373270966129123kg per1kgfinishedMgOH2. Keep105.79kg totalreferencebrine mass by using104.07159280039637kgwater; dissolvedMgCl2 andMgassays are DERIVED from this throughput/yield assumption,not observedsalarlakecomposition. Do not buy sodiumchloride as Mg feed or use MgCl2 cut-off coproducts from Ti/Zr/Hf sponge manufacture. Missing primaryMgCl2 supply is supplied through an explicit synthetic equivalent:MgO+2HCl-&gt;MgCl2+H2O,using real existingMgOmarket anddryHCl-equivalentmarket. This is an alternative primary chemical feed route,NOT a validated naturalbrine mining LCI; actual brine extraction/evaporation allocation may be substantially lower and requires a separate dataset.100%upstreamprecursorconversion with2MJheat+0.5kWh/kgdryMgCl2 allowance is explicit; rejectproduction,acidcarrierwater andgradepurification remain gaps. Its reactionwater is emitted as water after nominaldrying; acid market already uses dryHCl reference mass. Parent precipitation retains source1.78kWh,6.42MJwasteheat,land/freight coefficients andadds matched0.05263157894736836kgMgOH2solidreject to genericinertdisposal plus106.07469551766555kgaqueousCaCl2/carrierfiltrate to genericwastewatertreatment atassumed1000kg/m3. Saline-density5% andspecificbrinetreatment sensitivity required:genericwastewater is a treatmentproxy,not demonstrateddesalination or dissolvedMgdischargefate. No recoveredCaCl2salescredit,noMgmetal smelting andno inventedzero-upstream-magnesium. Active NMMT precursor purchase routes to thisnewreference at unchanged0.0275kg/kgactivepowder;legacyMgOH2provider retainedannotated fortraceability. Otherbattery recipes/capacitylearning unchanged; no native/runtime/YAML orprimary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C601" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D601" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E601" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F601" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G601" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H601" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I601" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium hydroxide production, precipitation</t>
-        </is>
-      </c>
-      <c r="B602">
-        <v>1</v>
-      </c>
-      <c r="C602" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F602" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G602" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
-        </is>
-      </c>
-      <c r="I602" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>market for lime, hydrated, loose weight</t>
-        </is>
-      </c>
-      <c r="B603">
-        <v>1.3373270966129123</v>
-      </c>
-      <c r="C603" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D603" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F603" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G603" t="inlineStr">
-        <is>
-          <t>lime, hydrated, loose weight</t>
-        </is>
-      </c>
-      <c r="I603" t="inlineStr">
-        <is>
-          <t>lime, hydrated, loose weight</t>
-        </is>
-      </c>
-    </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
-        </is>
-      </c>
-      <c r="B604">
-        <v>105.79</v>
-      </c>
-      <c r="C604" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F604" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G604" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
-        </is>
-      </c>
-      <c r="I604" t="inlineStr">
-        <is>
-          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>market for transport, freight, lorry, unspecified</t>
-        </is>
-      </c>
-      <c r="B605">
-        <v>0.12</v>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D605" t="inlineStr">
-        <is>
-          <t>ton kilometer</t>
-        </is>
-      </c>
-      <c r="F605" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G605" t="inlineStr">
-        <is>
-          <t>transport, freight, lorry, unspecified</t>
-        </is>
-      </c>
-      <c r="I605" t="inlineStr">
-        <is>
-          <t>transport, freight, lorry, unspecified</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B606">
-        <v>1.78</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>market group for transport, freight train</t>
+          <t xml:space="preserve">magnesium hydroxide production, precipitation</t>
         </is>
       </c>
       <c r="B607">
-        <v>0.717</v>
+        <v>1</v>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>ton kilometer</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>transport, freight train</t>
+          <t xml:space="preserve">magnesium hydroxide, precipitation</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>market for wastewater, average</t>
+          <t>market for lime, hydrated, loose weight</t>
         </is>
       </c>
       <c r="B608">
-        <v>-0.10607469551766555</v>
+        <v>1.3373270966129123</v>
       </c>
       <c r="C608" t="inlineStr">
         <is>
@@ -11438,7 +11327,7 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>cubic meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
@@ -11448,27 +11337,27 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>lime, hydrated, loose weight</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>lime, hydrated, loose weight</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>market for inert waste, for final disposal</t>
+          <t xml:space="preserve">magnesium brine production, with magnesium chloride</t>
         </is>
       </c>
       <c r="B609">
-        <v>-0.05263157894736836</v>
+        <v>105.79</v>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -11483,70 +11372,245 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>inert waste, for final disposal</t>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>inert waste, for final disposal</t>
+          <t xml:space="preserve">magnesium brine, with magnesium chloride</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Heat, waste</t>
+          <t>market for transport, freight, lorry, unspecified</t>
         </is>
       </c>
       <c r="B610">
-        <v>6.42</v>
+        <v>0.12</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>megajoule</t>
-        </is>
-      </c>
-      <c r="E610" t="inlineStr">
-        <is>
-          <t>air</t>
+          <t>ton kilometer</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>biosphere</t>
-        </is>
-      </c>
-      <c r="H610" t="inlineStr">
-        <is>
-          <t/>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B611">
+        <v>1.78</v>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>market group for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B612">
+        <v>0.717</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B613">
+        <v>-0.10607469551766555</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B614">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Heat, waste</t>
+        </is>
+      </c>
+      <c r="B615">
+        <v>6.42</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
           <t>Occupation, mineral extraction site</t>
         </is>
       </c>
-      <c r="B611">
+      <c r="B616">
         <v>1.63</v>
       </c>
-      <c r="D611" t="inlineStr">
+      <c r="D616" t="inlineStr">
         <is>
           <t>square meter-year</t>
         </is>
       </c>
-      <c r="E611" t="inlineStr">
+      <c r="E616" t="inlineStr">
         <is>
           <t>natural resource::land</t>
         </is>
       </c>
-      <c r="F611" t="inlineStr">
+      <c r="F616" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>
       </c>
-      <c r="H611" t="inlineStr">
+      <c r="H616" t="inlineStr">
         <is>
           <t/>
         </is>
